--- a/_bmad-output/QuantumRadar-Sprint-Tracker.xlsx
+++ b/_bmad-output/QuantumRadar-Sprint-Tracker.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Assignment" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Issues" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hướng dẫn" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Onboarding" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,8 +78,18 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -155,6 +166,21 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -182,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -262,6 +288,75 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2009,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2372,92 +2467,92 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>1R.1</t>
+          <t>E.1</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Epic 1</t>
+          <t>Epic E</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>1R Research</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>Đánh giá nguồn dữ liệu (Etherscan/Dune/Alchemy)</t>
+          <t>RPC &amp; API Credential Provisioning</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 1</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>backlog</t>
+          <t>ready-for-dev</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
         <is>
-          <t>[RESEARCH] So sánh Etherscan/Dune/Alchemy: rate limit, chi phí/tháng, độ sâu archival, hỗ trợ WSS. Chốt nguồn primary+fallback → research/data_sources.md; xác nhận lấy được block-range LUNA/FTX.</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="22" t="n"/>
+          <t>Lấy + điền WSS_URL (Alchemy/Infura) + ETHERSCAN_API_KEY vào .env. docs/environment_setup.md hướng dẫn từng bước (nơi lấy key, free-tier, rate limit). Smoke test: eth_subscribe nhận ≥1 block header; 1 call Etherscan HTTP 200. .env KHÔNG commit (chỉ .env.example).</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr"/>
+      <c r="M7" s="22" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>1R.2</t>
+          <t>E.2</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Epic 1</t>
+          <t>Epic E</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>1R Research</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>Đối chiếu Event Schema ↔ ABI thật</t>
+          <t>Contract &amp; Wallet Address Registry</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 1</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
@@ -2467,42 +2562,42 @@
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1B.3</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
         <is>
-          <t>[RESEARCH] Map từng event Uniswap V3 (Swap/Mint/Burn)+Aave V3 (Borrow/Supply/Withdraw/LiquidationCall) từ ABI chính thức sang tick_data.schema.json. Liệt kê field khớp/thiếu/cần thêm → research/schema_abi_gap.md. Đề xuất vá schema 0.1. CHẶN decoder 1B.</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="22" t="n"/>
+          <t>Điền địa chỉ mainnet thật vào contracts_whitelist.yaml: Uniswap V3 USDC/WETH 0x88e6A0..., Aave V2 Pool 0x7d2768..., Aave V3 Pool 0x87870B.... Mỗi entry có protocol, pool_meta, checksum hợp lệ + link Etherscan. load_whitelist() (1B.3) load không lỗi.</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr"/>
+      <c r="M8" s="22" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>1R.3</t>
+          <t>E.3</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Epic 1</t>
+          <t>Epic E</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>1R Research</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>Phương pháp gán nhãn Ground-Truth LUNA/FTX</t>
+          <t>Webhook Test Endpoint Config</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Quants</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
@@ -2512,52 +2607,52 @@
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 1</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>backlog</t>
+          <t>ready-for-dev</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
         <is>
-          <t>[RESEARCH] Định nghĩa tiêu chí 'cascade bắt đầu' &amp; 'RED deadline' cho LUNA (2022-05) &amp; FTX (2022-11) từ on-chain + tường thuật → research/ground_truth_labeling.md, đối chiếu fixtures README. CHẶN Epic 4 verify.</t>
-        </is>
-      </c>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="13" t="n"/>
-      <c r="M9" s="22" t="n"/>
+          <t>Cấu hình 1 webhook URL nhận thử (webhook.site HOẶC local echo tools.webhook_echo :9000). docs/environment_setup.md ghi cách lấy URL + đăng ký qua /subscribe. Gửi thử 1 payload mẫu khớp fragility_alert.schema.json. URL lưu WEBHOOK_TEST_URL trong .env.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr"/>
+      <c r="M9" s="22" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>1A.1</t>
+          <t>E.4</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Epic 1</t>
+          <t>Epic E</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>1A Realtime WS</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>Nạp cấu hình môi trường &amp; secrets</t>
+          <t>Environment Validation Script [BUILD]</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 1</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
@@ -2567,22 +2662,22 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 1</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>backlog</t>
+          <t>ready-for-dev</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>E.1, E.2, E.3</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
         <is>
-          <t>Tạo ingestion/config.py với Pydantic BaseSettings đọc từ .env: ALCHEMY_WSS_URL, INFURA_WSS_URL (fallback), CHAIN_ID (mặc định 1), RECONNECT_MAX_TRIES=7, BUFFER_SIZE=10, LOG_LEVEL=INFO. Tạo IngestionConfig dataclass typed. Nếu thiếu biến bắt buộc → raise ConfigError với message rõ ràng. Cung cấp .env.example. Unit test: load ok, thiếu URL raise, URL sai scheme raise.</t>
+          <t>python -m tools.check_env kiểm 5 mục: (1) biến bắt buộc, (2) WSS connect + nhận block, (3) Etherscan 200, (4) whitelist load, (5) webhook test nhận payload. Mỗi dòng ✅/❌ + gợi ý; exit 0 nếu PASS hết, 1 nếu FAIL. Chạy được ngay sau clone + cp .env.example .env (không traceback khi thiếu key).</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr"/>
@@ -2592,52 +2687,52 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>1A.2</t>
+          <t>E.5</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Epic 1</t>
+          <t>Epic E</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>1A Realtime WS</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>Wrapper AsyncWeb3 Client</t>
+          <t>Project Usage &amp; Git Workflow Guide</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 1</t>
+          <t>Tech Writer</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 1</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>backlog</t>
+          <t>ready-for-dev</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
-          <t>1A.1</t>
+          <t>E.1</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
         <is>
-          <t>Viết ingestion/web3_client.py bọc web3.AsyncWeb3 với WebSocketProvider. Expose method async connect(), disconnect(), is_connected. Timeout connect ≤ 3 giây, raise ConnectionTimeout nếu quá. Logging INFO khi connect thành công (endpoint, chain_id). Unit test dùng aioresponses hoặc mock_ws_server (0.5): connect ok, timeout, disconnect sạch.</t>
+          <t>docs/usage_guide.md: clone, cp .env.example .env, pip install -e '.[dev]', chạy pipeline (python -m ingestion.pipeline --source=mock), mock WSS, pytest. docs/git_workflow.md: git cơ bản (add/commit/push/pull, branch, conflict) + quy ước branch (feat/fix/chore) + commit convention + PR flow. Rà .gitignore che .env/__pycache__/.pytest_cache/*.log; CONTRIBUTING.md tóm tắt + link. Không secret bị commit.</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr"/>
@@ -2647,7 +2742,7 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>1A.3</t>
+          <t>1R.1</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -2657,17 +2752,17 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>1A Realtime WS</t>
+          <t>1R Research</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>Reconnector Exponential Backoff</t>
+          <t>Đánh giá nguồn dữ liệu (Etherscan/Dune/Alchemy)</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 1</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
@@ -2687,22 +2782,22 @@
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
-          <t>1A.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
         <is>
-          <t>Thêm decorator @with_retry_backoff cho web3_client. Chuỗi delay 0.5→1→2→4→8→16→30s (max 7 lần). Sau lần 7 raise MaxRetriesExceeded. Structured log JSON mỗi lần retry: {attempt, delay, error_type, error_msg}. Unit test: kill mock server giữa chừng → client reconnect đúng số lần và tiếp tục nhận block.</t>
-        </is>
-      </c>
-      <c r="K12" s="13" t="inlineStr"/>
-      <c r="L12" s="13" t="inlineStr"/>
-      <c r="M12" s="22" t="inlineStr"/>
+          <t>[RESEARCH] So sánh Etherscan/Dune/Alchemy: rate limit, chi phí/tháng, độ sâu archival, hỗ trợ WSS. Chốt nguồn primary+fallback → research/data_sources.md; xác nhận lấy được block-range LUNA/FTX.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="22" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>1A.4</t>
+          <t>1R.2</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -2712,22 +2807,22 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>1A Realtime WS</t>
+          <t>1R Research</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>Subscribe newHeads → async generator</t>
+          <t>Đối chiếu Event Schema ↔ ABI thật</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 1</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
@@ -2737,27 +2832,27 @@
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>backlog</t>
+          <t>ready-for-dev</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>1A.3, 0.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
         <is>
-          <t>Method subscribe_new_heads() trả về async generator yield BlockHeader dict. Log DEBUG mỗi block (number, hash, timestamp, drift_ms = now - block.timestamp*1000). Assertion: block_number tăng monotonic. Test integration với mock_ws_server ở speed=1x trong 60s: drift trung bình &lt; 100ms, không mất block.</t>
-        </is>
-      </c>
-      <c r="K13" s="13" t="inlineStr"/>
-      <c r="L13" s="13" t="inlineStr"/>
-      <c r="M13" s="22" t="inlineStr"/>
+          <t>[RESEARCH] Map từng event Uniswap V3 (Swap/Mint/Burn)+Aave V3 (Borrow/Supply/Withdraw/LiquidationCall) từ ABI chính thức sang tick_data.schema.json. Liệt kê field khớp/thiếu/cần thêm → research/schema_abi_gap.md. Đề xuất vá schema 0.1. CHẶN decoder 1B.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="22" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>1A.5</t>
+          <t>1R.3</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
@@ -2767,27 +2862,27 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>1A Realtime WS</t>
+          <t>1R Research</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>Heartbeat + Prometheus metrics</t>
+          <t>Phương pháp gán nhãn Ground-Truth LUNA/FTX</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 1</t>
+          <t>Quants</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -2797,22 +2892,22 @@
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
-          <t>1A.4</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
         <is>
-          <t>Expose /metrics endpoint (FastAPI mini app port 9101) với: ws_connected (gauge), ws_reconnects_total (counter), blocks_received_total (counter), block_drift_ms (histogram), last_block_seen_ts (gauge). Alert rule PromQL: nếu now - last_block_seen_ts &gt; 15s → firing. Test: force stop mock server 20s, verify metric last_block_seen_ts đứng yên và có thể trigger alert.</t>
-        </is>
-      </c>
-      <c r="K14" s="13" t="inlineStr"/>
-      <c r="L14" s="13" t="inlineStr"/>
-      <c r="M14" s="22" t="inlineStr"/>
+          <t>[RESEARCH] Định nghĩa tiêu chí 'cascade bắt đầu' &amp; 'RED deadline' cho LUNA (2022-05) &amp; FTX (2022-11) từ on-chain + tường thuật → research/ground_truth_labeling.md, đối chiếu fixtures README. CHẶN Epic 4 verify.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="22" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>1B.1</t>
+          <t>1A.1</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -2822,17 +2917,17 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>1B Event Decoding</t>
+          <t>1A Realtime WS</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>Decode sự kiện Uniswap V3</t>
+          <t>Nạp cấu hình môi trường &amp; secrets</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Engineer 1</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
@@ -2857,7 +2952,7 @@
       </c>
       <c r="J15" s="22" t="inlineStr">
         <is>
-          <t>Viết ingestion/decoders/uniswap_v3.py decode log raw thành Python dict theo schema 0.1. Xử lý 3 topic: Swap (0xc42079…), Mint (0x7a53080b…), Burn (0x0c396cd9…). Dùng ABI JSON commit trong repo. Test với 5 log thật từ mainnet (đã lưu snapshot JSON): output khớp field-by-field. Nếu decode fail → raise DecodeError, không crash.</t>
+          <t>Tạo ingestion/config.py với Pydantic BaseSettings đọc từ .env: ALCHEMY_WSS_URL, INFURA_WSS_URL (fallback), CHAIN_ID (mặc định 1), RECONNECT_MAX_TRIES=7, BUFFER_SIZE=10, LOG_LEVEL=INFO. Tạo IngestionConfig dataclass typed. Nếu thiếu biến bắt buộc → raise ConfigError với message rõ ràng. Cung cấp .env.example. Unit test: load ok, thiếu URL raise, URL sai scheme raise.</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr"/>
@@ -2867,7 +2962,7 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>1B.2</t>
+          <t>1A.2</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -2877,17 +2972,17 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>1B Event Decoding</t>
+          <t>1A Realtime WS</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>Decode sự kiện Aave V3</t>
+          <t>Wrapper AsyncWeb3 Client</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Engineer 1</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -2907,12 +3002,12 @@
       </c>
       <c r="I16" s="22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1A.1</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
         <is>
-          <t>Viết ingestion/decoders/aave_v3.py decode Borrow, Supply, Withdraw, LiquidationCall theo ABI Aave V3 Pool contract (0x87870Bca…). Chuyển raw uint256 amount về Decimal đúng số thập phân của token. Test với 5 log mainnet snapshot: khớp field. Xử lý cả trường hợp reserve token có 6 decimals (USDC) và 18 decimals (WETH).</t>
+          <t>Viết ingestion/web3_client.py bọc web3.AsyncWeb3 với WebSocketProvider. Expose method async connect(), disconnect(), is_connected. Timeout connect ≤ 3 giây, raise ConnectionTimeout nếu quá. Logging INFO khi connect thành công (endpoint, chain_id). Unit test dùng aioresponses hoặc mock_ws_server (0.5): connect ok, timeout, disconnect sạch.</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr"/>
@@ -2922,7 +3017,7 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>1B.3</t>
+          <t>1A.3</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -2932,17 +3027,17 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>1B Event Decoding</t>
+          <t>1A Realtime WS</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>Whitelist địa chỉ contract</t>
+          <t>Reconnector Exponential Backoff</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Engineer 1</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
@@ -2962,12 +3057,12 @@
       </c>
       <c r="I17" s="22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1A.2</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
         <is>
-          <t>Tạo config/contracts_whitelist.yaml chứa 3-5 pool Uniswap V3 (USDC/ETH, WBTC/ETH, USDT/ETH) + Aave V3 Pool. Mỗi entry: address (checksum), protocol, pool_name, base_token, quote_token, deployed_block. Loader validate checksum bằng eth_utils.to_checksum_address(). Unit test: file load ok, address sai checksum raise, empty file raise.</t>
+          <t>Thêm decorator @with_retry_backoff cho web3_client. Chuỗi delay 0.5→1→2→4→8→16→30s (max 7 lần). Sau lần 7 raise MaxRetriesExceeded. Structured log JSON mỗi lần retry: {attempt, delay, error_type, error_msg}. Unit test: kill mock server giữa chừng → client reconnect đúng số lần và tiếp tục nhận block.</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr"/>
@@ -2977,7 +3072,7 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>1B.4</t>
+          <t>1A.4</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -2987,17 +3082,17 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>1B Event Decoding</t>
+          <t>1A Realtime WS</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>Router &amp; Normalizer sự kiện</t>
+          <t>Subscribe newHeads → async generator</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Engineer 1</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
@@ -3007,7 +3102,7 @@
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
@@ -3017,12 +3112,12 @@
       </c>
       <c r="I18" s="22" t="inlineStr">
         <is>
-          <t>1B.1, 1B.2, 1B.3</t>
+          <t>1A.3, 0.5</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>Viết ingestion/router.py nhận raw log, kiểm tra address có trong whitelist không, chọn decoder (Uniswap|Aave) theo protocol, gọi decode, produce TickDataEvent (dataclass tuân schema 0.1). Log không whitelist → drop (log DEBUG, tăng counter events_dropped). Test: feed 100 log hỗn hợp → đúng số output, đúng phân loại, không leak log ngoài whitelist.</t>
+          <t>Method subscribe_new_heads() trả về async generator yield BlockHeader dict. Log DEBUG mỗi block (number, hash, timestamp, drift_ms = now - block.timestamp*1000). Assertion: block_number tăng monotonic. Test integration với mock_ws_server ở speed=1x trong 60s: drift trung bình &lt; 100ms, không mất block.</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr"/>
@@ -3032,7 +3127,7 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>1C.1</t>
+          <t>1A.5</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -3042,27 +3137,27 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>1C Ring Buffer</t>
+          <t>1A Realtime WS</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>Interface trừu tượng Ring Buffer</t>
+          <t>Heartbeat + Prometheus metrics</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 3</t>
+          <t>Data Engineer 1</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
@@ -3072,12 +3167,12 @@
       </c>
       <c r="I19" s="22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1A.4</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
         <is>
-          <t>Viết core/ring_buffer/base.py với abstract class RingBuffer[T]: push(item), snapshot() -&gt; list[T], __len__, capacity, is_full. Docstring nêu bất biến: FIFO drop-oldest, thread-unsafe by default, in-memory only. Test contract: fill vượt capacity → drop từ đầu, snapshot trả về list đúng thứ tự chèn.</t>
+          <t>Expose /metrics endpoint (FastAPI mini app port 9101) với: ws_connected (gauge), ws_reconnects_total (counter), blocks_received_total (counter), block_drift_ms (histogram), last_block_seen_ts (gauge). Alert rule PromQL: nếu now - last_block_seen_ts &gt; 15s → firing. Test: force stop mock server 20s, verify metric last_block_seen_ts đứng yên và có thể trigger alert.</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr"/>
@@ -3087,7 +3182,7 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>1C.2</t>
+          <t>1B.1</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -3097,17 +3192,17 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>1C Ring Buffer</t>
+          <t>1B Event Decoding</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>Cài đặt Ring Buffer bằng collections.deque</t>
+          <t>Decode sự kiện Uniswap V3</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 3</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
@@ -3127,12 +3222,12 @@
       </c>
       <c r="I20" s="22" t="inlineStr">
         <is>
-          <t>1C.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>Viết DequeRingBuffer(RingBuffer) dùng collections.deque(maxlen=capacity). Benchmark micro với pytest-benchmark: push &lt; 1μs/op ở capacity=10 trên MacBook M-series. Test: push 1000 item → chỉ giữ 10 cuối, thứ tự đúng. Verify không tạo memory leak sau 10^6 push (memory_profiler).</t>
+          <t>Viết ingestion/decoders/uniswap_v3.py decode log raw thành Python dict theo schema 0.1. Xử lý 3 topic: Swap (0xc42079…), Mint (0x7a53080b…), Burn (0x0c396cd9…). Dùng ABI JSON commit trong repo. Test với 5 log thật từ mainnet (đã lưu snapshot JSON): output khớp field-by-field. Nếu decode fail → raise DecodeError, không crash.</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr"/>
@@ -3142,7 +3237,7 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>1C.3</t>
+          <t>1B.2</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -3152,27 +3247,27 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>1C Ring Buffer</t>
+          <t>1B Event Decoding</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>Variant Numpy static array</t>
+          <t>Decode sự kiện Aave V3</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 3</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -3182,12 +3277,12 @@
       </c>
       <c r="I21" s="22" t="inlineStr">
         <is>
-          <t>1C.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
         <is>
-          <t>Viết NumpyRingBuffer(RingBuffer) dùng np.ndarray + head pointer index. Cả 2 variant chạy chung contract test của 1C.1. Benchmark so sánh 1C.2 vs 1C.3 trên 10^5 push + snapshot: report vào metrics/ring_buffer_bench.md để chọn variant chính thức.</t>
+          <t>Viết ingestion/decoders/aave_v3.py decode Borrow, Supply, Withdraw, LiquidationCall theo ABI Aave V3 Pool contract (0x87870Bca…). Chuyển raw uint256 amount về Decimal đúng số thập phân của token. Test với 5 log mainnet snapshot: khớp field. Xử lý cả trường hợp reserve token có 6 decimals (USDC) và 18 decimals (WETH).</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr"/>
@@ -3197,7 +3292,7 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>1C.4</t>
+          <t>1B.3</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -3207,17 +3302,17 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>1C Ring Buffer</t>
+          <t>1B Event Decoding</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>Wrapper asyncio-safe</t>
+          <t>Whitelist địa chỉ contract</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 3</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -3227,7 +3322,7 @@
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
@@ -3237,12 +3332,12 @@
       </c>
       <c r="I22" s="22" t="inlineStr">
         <is>
-          <t>1C.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
         <is>
-          <t>Bọc RingBuffer trong AsyncSafeRingBuffer dùng asyncio.Lock. Method async apush(), async asnapshot(). Test stress: 4 producer coroutine + 2 consumer chạy 10s → không race, count push = count observed, overhead &lt; 5% so với sync (benchmark).</t>
+          <t>Tạo config/contracts_whitelist.yaml chứa 3-5 pool Uniswap V3 (USDC/ETH, WBTC/ETH, USDT/ETH) + Aave V3 Pool. Mỗi entry: address (checksum), protocol, pool_name, base_token, quote_token, deployed_block. Loader validate checksum bằng eth_utils.to_checksum_address(). Unit test: file load ok, address sai checksum raise, empty file raise.</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr"/>
@@ -3252,7 +3347,7 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>1D.1</t>
+          <t>1B.4</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -3262,17 +3357,17 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>1D CSV Historical</t>
+          <t>1B Event Decoding</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>Mapping CSV → TickDataEvent</t>
+          <t>Router &amp; Normalizer sự kiện</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
@@ -3282,7 +3377,7 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -3292,12 +3387,12 @@
       </c>
       <c r="I23" s="22" t="inlineStr">
         <is>
-          <t>0.1, 0.4</t>
+          <t>1B.1, 1B.2, 1B.3</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
         <is>
-          <t>Viết ingestion/csv/mapper.py đọc 1 row (dict từ csv.DictReader) → TickDataEvent theo schema 0.1. Xử lý type coercion: str→Decimal cho amount, str→datetime cho timestamp. Row hỏng: log WARNING kèm row_number + reason, không crash. Test với fixtures 0.4: 100% row luna_ust parse ok, cố tình chèn row lỗi vẫn stream tiếp.</t>
+          <t>Viết ingestion/router.py nhận raw log, kiểm tra address có trong whitelist không, chọn decoder (Uniswap|Aave) theo protocol, gọi decode, produce TickDataEvent (dataclass tuân schema 0.1). Log không whitelist → drop (log DEBUG, tăng counter events_dropped). Test: feed 100 log hỗn hợp → đúng số output, đúng phân loại, không leak log ngoài whitelist.</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr"/>
@@ -3307,7 +3402,7 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>1D.2</t>
+          <t>1C.1</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -3317,17 +3412,17 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>1D CSV Historical</t>
+          <t>1C Ring Buffer</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>CSV Streamer async</t>
+          <t>Interface trừu tượng Ring Buffer</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 3</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -3347,12 +3442,12 @@
       </c>
       <c r="I24" s="22" t="inlineStr">
         <is>
-          <t>1D.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
         <is>
-          <t>Viết async def stream_csv(path) -&gt; AsyncGenerator[TickDataEvent] dùng aiofiles đọc từng chunk. Không load full file vào RAM. Verify với fixture 5000 dòng: memory peak &lt; 50MB (tracemalloc). Test yield count đúng số row hợp lệ.</t>
+          <t>Viết core/ring_buffer/base.py với abstract class RingBuffer[T]: push(item), snapshot() -&gt; list[T], __len__, capacity, is_full. Docstring nêu bất biến: FIFO drop-oldest, thread-unsafe by default, in-memory only. Test contract: fill vượt capacity → drop từ đầu, snapshot trả về list đúng thứ tự chèn.</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr"/>
@@ -3362,7 +3457,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>1D.3</t>
+          <t>1C.2</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -3372,17 +3467,17 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>1D CSV Historical</t>
+          <t>1C Ring Buffer</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
         <is>
-          <t>Backtest Replay Driver</t>
+          <t>Cài đặt Ring Buffer bằng collections.deque</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 3</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
@@ -3392,7 +3487,7 @@
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -3402,12 +3497,12 @@
       </c>
       <c r="I25" s="22" t="inlineStr">
         <is>
-          <t>1D.2, 1C.4</t>
+          <t>1C.1</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
         <is>
-          <t>Viết ingestion/csv/replay.py: nhận path CSV + rate (1x=realtime theo timestamp gap, 100x=nhanh 100 lần, asap=không delay). Feed vào RingBuffer. CLI wrapper: python -m ingestion.csv.replay --file luna.csv --rate 100x. Test: file 5 phút wall-clock ở rate=1x mất ~5 phút (±5%), rate=asap mất &lt; 10s.</t>
+          <t>Viết DequeRingBuffer(RingBuffer) dùng collections.deque(maxlen=capacity). Benchmark micro với pytest-benchmark: push &lt; 1μs/op ở capacity=10 trên MacBook M-series. Test: push 1000 item → chỉ giữ 10 cuối, thứ tự đúng. Verify không tạo memory leak sau 10^6 push (memory_profiler).</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr"/>
@@ -3417,7 +3512,7 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>1E.1</t>
+          <t>1C.3</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -3427,22 +3522,22 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>1E Integration</t>
+          <t>1C Ring Buffer</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>Pipeline Orchestrator</t>
+          <t>Variant Numpy static array</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>Data Engineer 1</t>
+          <t>Data Engineer 3</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
@@ -3457,12 +3552,12 @@
       </c>
       <c r="I26" s="22" t="inlineStr">
         <is>
-          <t>1A.4, 1B.4, 1C.4</t>
+          <t>1C.1</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
         <is>
-          <t>Viết ingestion/pipeline.py IngestionPipeline.run() ghép: WS client (1A) → decoder+router (1B) → ring buffer (1C). Handle SIGTERM: drain event trong queue &lt; 2s rồi exit code 0. Log INFO khởi động + shutdown timing. E2E test dùng mock server 0.5 chạy 60s: throughput đúng, không mất event, shutdown sạch.</t>
+          <t>Viết NumpyRingBuffer(RingBuffer) dùng np.ndarray + head pointer index. Cả 2 variant chạy chung contract test của 1C.1. Benchmark so sánh 1C.2 vs 1C.3 trên 10^5 push + snapshot: report vào metrics/ring_buffer_bench.md để chọn variant chính thức.</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr"/>
@@ -3472,7 +3567,7 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>1E.2</t>
+          <t>1C.4</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -3482,22 +3577,22 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>1E Integration</t>
+          <t>1C Ring Buffer</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
         <is>
-          <t>Tool đối chiếu Etherscan</t>
+          <t>Wrapper asyncio-safe</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer 3</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
@@ -3512,12 +3607,12 @@
       </c>
       <c r="I27" s="22" t="inlineStr">
         <is>
-          <t>1E.1</t>
+          <t>1C.2</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
         <is>
-          <t>Viết tools/reconcile_etherscan.py: chạy pipeline 5 phút live, lưu event vào file JSONL, sau đó gọi Etherscan API (getLogs cho cùng block range) và so sánh field-by-field. AC: 3 block ngẫu nhiên có 100% event match. Report tỷ lệ match &lt; 99.5% → exit code 1 (CI fail).</t>
+          <t>Bọc RingBuffer trong AsyncSafeRingBuffer dùng asyncio.Lock. Method async apush(), async asnapshot(). Test stress: 4 producer coroutine + 2 consumer chạy 10s → không race, count push = count observed, overhead &lt; 5% so với sync (benchmark).</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr"/>
@@ -3527,7 +3622,7 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>1E.3</t>
+          <t>1D.1</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
@@ -3537,27 +3632,27 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>1E Integration</t>
+          <t>1D CSV Historical</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>Báo cáo Data Quality Profiling</t>
+          <t>Mapping CSV → TickDataEvent</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -3567,12 +3662,12 @@
       </c>
       <c r="I28" s="22" t="inlineStr">
         <is>
-          <t>1E.1</t>
+          <t>0.1, 0.4</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
         <is>
-          <t>Viết tools/profile_data_quality.py: đọc log JSONL 24h, sinh HTML report gồm 4 biểu đồ (throughput theo phút, latency drift histogram, event type distribution, protocol distribution) + bảng flag các gap &gt; 30s. Dùng pandas + plotly. Đưa vào lịch chạy hàng đêm.</t>
+          <t>Viết ingestion/csv/mapper.py đọc 1 row (dict từ csv.DictReader) → TickDataEvent theo schema 0.1. Xử lý type coercion: str→Decimal cho amount, str→datetime cho timestamp. Row hỏng: log WARNING kèm row_number + reason, không crash. Test với fixtures 0.4: 100% row luna_ust parse ok, cố tình chèn row lỗi vẫn stream tiếp.</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr"/>
@@ -3582,32 +3677,32 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2R.1</t>
+          <t>1D.2</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Epic 2</t>
+          <t>Epic 1</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>2R Research</t>
+          <t>1D CSV Historical</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>Catalog &amp; nguồn Node Feature</t>
+          <t>CSV Streamer async</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 2</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
@@ -3617,102 +3712,102 @@
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>ready-for-dev</t>
+          <t>backlog</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1D.1</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
         <is>
-          <t>[RESEARCH] Mỗi feature (tvl, utilization, price_delta, volatility, borrow_rate): công thức, input event/field, đơn vị, range, missing-data policy → research/feature_catalog.md. Chỉ rõ feature nào từ schema 0.1, feature nào cần nguồn phụ. CHẶN 2B.2.</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="n"/>
-      <c r="L29" s="13" t="n"/>
-      <c r="M29" s="22" t="n"/>
+          <t>Viết async def stream_csv(path) -&gt; AsyncGenerator[TickDataEvent] dùng aiofiles đọc từng chunk. Không load full file vào RAM. Verify với fixture 5000 dòng: memory peak &lt; 50MB (tracemalloc). Test yield count đúng số row hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr"/>
+      <c r="L29" s="13" t="inlineStr"/>
+      <c r="M29" s="22" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>2R.2</t>
+          <t>1D.3</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Epic 2</t>
+          <t>Epic 1</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>2R Research</t>
+          <t>1D CSV Historical</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>Thiết kế Graph Topology</t>
+          <t>Backtest Replay Driver</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 1</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>ready-for-dev</t>
+          <t>backlog</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
         <is>
-          <t>0.2, 1B.3</t>
+          <t>1D.2, 1C.4</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
         <is>
-          <t>[RESEARCH] Chốt loại node, quy tắc nối cạnh, N kỳ vọng runtime, độ thưa cho scope 3-5 pool → research/graph_topology.md (sơ đồ mẫu, N ước lượng, sparsity). Khuyến nghị dense/sparse v1. CHẶN tensor shape 2B.*.</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="n"/>
-      <c r="L30" s="13" t="n"/>
-      <c r="M30" s="22" t="n"/>
+          <t>Viết ingestion/csv/replay.py: nhận path CSV + rate (1x=realtime theo timestamp gap, 100x=nhanh 100 lần, asap=không delay). Feed vào RingBuffer. CLI wrapper: python -m ingestion.csv.replay --file luna.csv --rate 100x. Test: file 5 phút wall-clock ở rate=1x mất ~5 phút (±5%), rate=asap mất &lt; 10s.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr"/>
+      <c r="L30" s="13" t="inlineStr"/>
+      <c r="M30" s="22" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>2A.1</t>
+          <t>1E.1</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Epic 2</t>
+          <t>Epic 1</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>2A Graph</t>
+          <t>1E Integration</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t>Schema Node Type</t>
+          <t>Pipeline Orchestrator</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 1</t>
+          <t>Data Engineer 1</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -3722,7 +3817,7 @@
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
@@ -3732,12 +3827,12 @@
       </c>
       <c r="I31" s="22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1A.4, 1B.4, 1C.4</t>
         </is>
       </c>
       <c r="J31" s="22" t="inlineStr">
         <is>
-          <t>Viết engine/graph/nodes.py Pydantic model: ProtocolNode, PoolNode, TokenNode với field theo schema 0.2. Ràng buộc: tvl ≥ 0, volatility ≥ 0, connectivity ∈ [0,1]. Validation error → raise. Unit test: model_validate ok với sample từ graph_example.json (0.2).</t>
+          <t>Viết ingestion/pipeline.py IngestionPipeline.run() ghép: WS client (1A) → decoder+router (1B) → ring buffer (1C). Handle SIGTERM: drain event trong queue &lt; 2s rồi exit code 0. Log INFO khởi động + shutdown timing. E2E test dùng mock server 0.5 chạy 60s: throughput đúng, không mất event, shutdown sạch.</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr"/>
@@ -3747,37 +3842,37 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>2A.2</t>
+          <t>1E.2</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>Epic 2</t>
+          <t>Epic 1</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>2A Graph</t>
+          <t>1E Integration</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
         <is>
-          <t>Schema Edge Type</t>
+          <t>Tool đối chiếu Etherscan</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 1</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -3787,12 +3882,12 @@
       </c>
       <c r="I32" s="22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1E.1</t>
         </is>
       </c>
       <c r="J32" s="22" t="inlineStr">
         <is>
-          <t>Viết engine/graph/edges.py: LiquidityFlowEdge, BorrowPositionEdge, SharedCollateralEdge. Ràng buộc: weight ∈ [0,1], source ≠ target, source/target phải tồn tại trong node list (validate ở graph level). Unit test model_validate + reject self-loop.</t>
+          <t>Viết tools/reconcile_etherscan.py: chạy pipeline 5 phút live, lưu event vào file JSONL, sau đó gọi Etherscan API (getLogs cho cùng block range) và so sánh field-by-field. AC: 3 block ngẫu nhiên có 100% event match. Report tỷ lệ match &lt; 99.5% → exit code 1 (CI fail).</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr"/>
@@ -3802,37 +3897,37 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>2A.3</t>
+          <t>1E.3</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Epic 2</t>
+          <t>Epic 1</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>2A Graph</t>
+          <t>1E Integration</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>Graph Builder JSON → NetworkX</t>
+          <t>Báo cáo Data Quality Profiling</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 1</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -3842,12 +3937,12 @@
       </c>
       <c r="I33" s="22" t="inlineStr">
         <is>
-          <t>2A.1, 2A.2, 0.4</t>
+          <t>1E.1</t>
         </is>
       </c>
       <c r="J33" s="22" t="inlineStr">
         <is>
-          <t>Viết engine/graph/builder.py: build_graph(events: list[TickDataEvent]) -&gt; networkx.MultiDiGraph gom event theo window (mặc định 60s), sinh node/edge theo type. Đảm bảo deterministic (cùng input → cùng graph). Benchmark: 1000 event → &lt; 20ms trên CPU M-series. Test dùng fixture 0.4 luna: sinh graph có ≥ 3 protocol, ≥ 10 pool, &gt; 20 edge.</t>
+          <t>Viết tools/profile_data_quality.py: đọc log JSONL 24h, sinh HTML report gồm 4 biểu đồ (throughput theo phút, latency drift histogram, event type distribution, protocol distribution) + bảng flag các gap &gt; 30s. Dùng pandas + plotly. Đưa vào lịch chạy hàng đêm.</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr"/>
@@ -3857,7 +3952,7 @@
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>2A.4</t>
+          <t>2R.1</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
@@ -3867,52 +3962,52 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>2A Graph</t>
+          <t>2R Research</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>Công thức trọng số cạnh</t>
+          <t>Catalog &amp; nguồn Node Feature</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 1 + Quants</t>
+          <t>AI Engineer 2</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
-          <t>backlog</t>
+          <t>ready-for-dev</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
         <is>
-          <t>2A.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J34" s="22" t="inlineStr">
         <is>
-          <t>Định nghĩa weight = normalize( volume_usd × exp(-λ × age_seconds) ) với λ=1/1800 (half-life 30 phút). Normalize theo min-max trong window. Doc công thức + rationale trong docs/graph_weight.md. Test: 2 event cùng volume nhưng lệch time → event mới có weight &gt; event cũ, cả hai ∈ [0,1].</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="inlineStr"/>
-      <c r="L34" s="13" t="inlineStr"/>
-      <c r="M34" s="22" t="inlineStr"/>
+          <t>[RESEARCH] Mỗi feature (tvl, utilization, price_delta, volatility, borrow_rate): công thức, input event/field, đơn vị, range, missing-data policy → research/feature_catalog.md. Chỉ rõ feature nào từ schema 0.1, feature nào cần nguồn phụ. CHẶN 2B.2.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n"/>
+      <c r="L34" s="13" t="n"/>
+      <c r="M34" s="22" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>2B.1</t>
+          <t>2R.2</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -3922,22 +4017,22 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>2B Tensor Map</t>
+          <t>2R Research</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
         <is>
-          <t>Constructor Adjacency Tensor</t>
+          <t>Thiết kế Graph Topology</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 2</t>
+          <t>AI Engineer 1</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
@@ -3947,27 +4042,27 @@
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>backlog</t>
+          <t>ready-for-dev</t>
         </is>
       </c>
       <c r="I35" s="22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.2, 1B.3</t>
         </is>
       </c>
       <c r="J35" s="22" t="inlineStr">
         <is>
-          <t>Viết engine/tensor/adjacency.py: build_adjacency(graph) -&gt; torch.Tensor shape (N,N) dtype=float32, symmetric (A + A.T)/2. Deterministic node ordering (sort theo node.id). Bench &lt; 5ms cho N=50. Test: A[i,j] == A[j,i]; row-sum &gt; 0 với node có edge; identity check với graph rỗng trả về zeros.</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="inlineStr"/>
-      <c r="L35" s="13" t="inlineStr"/>
-      <c r="M35" s="22" t="inlineStr"/>
+          <t>[RESEARCH] Chốt loại node, quy tắc nối cạnh, N kỳ vọng runtime, độ thưa cho scope 3-5 pool → research/graph_topology.md (sơ đồ mẫu, N ước lượng, sparsity). Khuyến nghị dense/sparse v1. CHẶN tensor shape 2B.*.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n"/>
+      <c r="L35" s="13" t="n"/>
+      <c r="M35" s="22" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>2B.2</t>
+          <t>2A.1</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
@@ -3977,17 +4072,17 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>2B Tensor Map</t>
+          <t>2A Graph</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
         <is>
-          <t>Node Feature Tensor</t>
+          <t>Schema Node Type</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 2</t>
+          <t>AI Engineer 1</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -4012,7 +4107,7 @@
       </c>
       <c r="J36" s="22" t="inlineStr">
         <is>
-          <t>Viết build_node_features(graph) -&gt; torch.Tensor shape (N, 5) gồm 5 feature: tvl_log, volume_24h_log, price_z, volatility, connectivity. Xử lý NaN → 0 và log WARNING kèm node_id. Test: kích thước đúng, không có NaN sau xử lý, log warning được emit đúng số lần.</t>
+          <t>Viết engine/graph/nodes.py Pydantic model: ProtocolNode, PoolNode, TokenNode với field theo schema 0.2. Ràng buộc: tvl ≥ 0, volatility ≥ 0, connectivity ∈ [0,1]. Validation error → raise. Unit test: model_validate ok với sample từ graph_example.json (0.2).</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr"/>
@@ -4022,7 +4117,7 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>2B.3</t>
+          <t>2A.2</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -4032,17 +4127,17 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>2B Tensor Map</t>
+          <t>2A Graph</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
         <is>
-          <t>Lớp Normalization</t>
+          <t>Schema Edge Type</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 2</t>
+          <t>AI Engineer 1</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
@@ -4052,7 +4147,7 @@
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -4062,12 +4157,12 @@
       </c>
       <c r="I37" s="22" t="inlineStr">
         <is>
-          <t>2B.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J37" s="22" t="inlineStr">
         <is>
-          <t>Viết engine/tensor/normalize.py hỗ trợ 2 mode: minmax (0-1) và zscore (mean 0 std 1), toggle qua config. Persist NormalizationState (min/max/mean/std) ra file để inference dùng lại. Test: forward + inverse trả về giá trị gốc (tolerance 1e-6), persist/load ok.</t>
+          <t>Viết engine/graph/edges.py: LiquidityFlowEdge, BorrowPositionEdge, SharedCollateralEdge. Ràng buộc: weight ∈ [0,1], source ≠ target, source/target phải tồn tại trong node list (validate ở graph level). Unit test model_validate + reject self-loop.</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr"/>
@@ -4077,7 +4172,7 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>2B.4</t>
+          <t>2A.3</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
@@ -4087,27 +4182,27 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>2B Tensor Map</t>
+          <t>2A Graph</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
         <is>
-          <t>Variant Sparse Tensor</t>
+          <t>Graph Builder JSON → NetworkX</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 2</t>
+          <t>AI Engineer 1</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -4117,12 +4212,12 @@
       </c>
       <c r="I38" s="22" t="inlineStr">
         <is>
-          <t>2B.1</t>
+          <t>2A.1, 2A.2, 0.4</t>
         </is>
       </c>
       <c r="J38" s="22" t="inlineStr">
         <is>
-          <t>Viết SparseAdjacencyTensor dùng torch.sparse_coo_tensor cho N &gt; 200. Benchmark: RAM giảm ≥ 80% so với dense; output dense.to_dense() khớp dense variant tolerance 1e-6. Config auto-switch: N ≥ 200 dùng sparse, ngược lại dense.</t>
+          <t>Viết engine/graph/builder.py: build_graph(events: list[TickDataEvent]) -&gt; networkx.MultiDiGraph gom event theo window (mặc định 60s), sinh node/edge theo type. Đảm bảo deterministic (cùng input → cùng graph). Benchmark: 1000 event → &lt; 20ms trên CPU M-series. Test dùng fixture 0.4 luna: sinh graph có ≥ 3 protocol, ≥ 10 pool, &gt; 20 edge.</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr"/>
@@ -4132,7 +4227,7 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>2C.1</t>
+          <t>2A.4</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -4142,17 +4237,17 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>2C Validation</t>
+          <t>2A Graph</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
         <is>
-          <t>Unit test invariant Tensor</t>
+          <t>Công thức trọng số cạnh</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>Quants</t>
+          <t>AI Engineer 1 + Quants</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -4172,12 +4267,12 @@
       </c>
       <c r="I39" s="22" t="inlineStr">
         <is>
-          <t>2B.1, 2B.2</t>
+          <t>2A.3</t>
         </is>
       </c>
       <c r="J39" s="22" t="inlineStr">
         <is>
-          <t>Viết test suite property-based dùng hypothesis: symmetry adjacency (∀ graph, A == A.T), non-negative feature (tvl, volume ≥ 0), mass conservation (sum flow-in ≈ sum flow-out tolerance 1%). Chạy 500 case random. Fail phải xuất minimal counter-example.</t>
+          <t>Định nghĩa weight = normalize( volume_usd × exp(-λ × age_seconds) ) với λ=1/1800 (half-life 30 phút). Normalize theo min-max trong window. Doc công thức + rationale trong docs/graph_weight.md. Test: 2 event cùng volume nhưng lệch time → event mới có weight &gt; event cũ, cả hai ∈ [0,1].</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr"/>
@@ -4187,7 +4282,7 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>2C.2</t>
+          <t>2B.1</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -4197,27 +4292,27 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>2C Validation</t>
+          <t>2B Tensor Map</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
         <is>
-          <t>Visualization Heatmap</t>
+          <t>Constructor Adjacency Tensor</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>Quants</t>
+          <t>AI Engineer 2</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
@@ -4227,12 +4322,12 @@
       </c>
       <c r="I40" s="22" t="inlineStr">
         <is>
-          <t>2A.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J40" s="22" t="inlineStr">
         <is>
-          <t>Viết tools/plot_adjacency.py: nhận graph snapshot → sinh heatmap.png (matplotlib) + heatmap_legend.json ghi mapping index→node.id. Config colormap (mặc định viridis). CI job: chạy trên 1 snapshot LUNA, upload artifact.</t>
+          <t>Viết engine/tensor/adjacency.py: build_adjacency(graph) -&gt; torch.Tensor shape (N,N) dtype=float32, symmetric (A + A.T)/2. Deterministic node ordering (sort theo node.id). Bench &lt; 5ms cho N=50. Test: A[i,j] == A[j,i]; row-sum &gt; 0 với node có edge; identity check với graph rỗng trả về zeros.</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr"/>
@@ -4242,7 +4337,7 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>2C.3</t>
+          <t>2B.2</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -4252,27 +4347,27 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>2C Validation</t>
+          <t>2B Tensor Map</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
         <is>
-          <t>So sánh với dữ liệu reference</t>
+          <t>Node Feature Tensor</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>Quants</t>
+          <t>AI Engineer 2</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
@@ -4282,12 +4377,12 @@
       </c>
       <c r="I41" s="22" t="inlineStr">
         <is>
-          <t>2A.3, 0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J41" s="22" t="inlineStr">
         <is>
-          <t>Lấy top-10 pool theo TVL từ Nansen/Dune public (query id đính kèm) làm reference. So sánh với top-10 edge weight cao nhất sinh từ builder trên cùng thời điểm LUNA t0. AC: ≥ 7/10 pool trùng. Report vào docs/graph_validation.md.</t>
+          <t>Viết build_node_features(graph) -&gt; torch.Tensor shape (N, 5) gồm 5 feature: tvl_log, volume_24h_log, price_z, volatility, connectivity. Xử lý NaN → 0 và log WARNING kèm node_id. Test: kích thước đúng, không có NaN sau xử lý, log warning được emit đúng số lần.</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr"/>
@@ -4297,92 +4392,92 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>3R.1</t>
+          <t>2B.3</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Epic 3</t>
+          <t>Epic 2</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>3R Research</t>
+          <t>2B Tensor Map</t>
         </is>
       </c>
       <c r="D42" s="22" t="inlineStr">
         <is>
-          <t>Đặc tả toán MPS→Fragility (TIÊN QUYẾT)</t>
+          <t>Lớp Normalization</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>AI Lead + Quants</t>
+          <t>AI Engineer 2</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
-          <t>ready-for-dev</t>
+          <t>backlog</t>
         </is>
       </c>
       <c r="I42" s="22" t="inlineStr">
         <is>
-          <t>0.2, 2B.1</t>
+          <t>2B.2</t>
         </is>
       </c>
       <c r="J42" s="22" t="inlineStr">
         <is>
-          <t>[RESEARCH][TIÊN QUYẾT] Đặc tả chính thức: adjacency+feature tensor → phân rã MPS/tensor-train → entanglement entropy → Fragility raw. Ký hiệu, chiều tensor, thứ tự contraction, công thức entropy, ánh xạ entropy→Fragility. Kèm ví dụ 3-node tính tay làm test oracle cho 3A.1 → research/mps_fragility_model.md. CHẶN TOÀN BỘ Epic 3.</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="n"/>
-      <c r="L42" s="13" t="n"/>
-      <c r="M42" s="22" t="n"/>
+          <t>Viết engine/tensor/normalize.py hỗ trợ 2 mode: minmax (0-1) và zscore (mean 0 std 1), toggle qua config. Persist NormalizationState (min/max/mean/std) ra file để inference dùng lại. Test: forward + inverse trả về giá trị gốc (tolerance 1e-6), persist/load ok.</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr"/>
+      <c r="L42" s="13" t="inlineStr"/>
+      <c r="M42" s="22" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>3R.2</t>
+          <t>2B.4</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Epic 3</t>
+          <t>Epic 2</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>3R Research</t>
+          <t>2B Tensor Map</t>
         </is>
       </c>
       <c r="D43" s="22" t="inlineStr">
         <is>
-          <t>Literature Review Tensor-Network Risk</t>
+          <t>Variant Sparse Tensor</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>Quants</t>
+          <t>AI Engineer 2</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
@@ -4392,37 +4487,37 @@
       </c>
       <c r="I43" s="22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2B.1</t>
         </is>
       </c>
       <c r="J43" s="22" t="inlineStr">
         <is>
-          <t>[RESEARCH] Khảo sát ≥5 nguồn về entanglement entropy làm proxy rủi ro &amp; tensor network trong tài chính. Tóm tắt+trích dẫn+bài học+giả định chưa có tiền lệ → research/literature_review.md.</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="n"/>
-      <c r="L43" s="13" t="n"/>
-      <c r="M43" s="22" t="n"/>
+          <t>Viết SparseAdjacencyTensor dùng torch.sparse_coo_tensor cho N &gt; 200. Benchmark: RAM giảm ≥ 80% so với dense; output dense.to_dense() khớp dense variant tolerance 1e-6. Config auto-switch: N ≥ 200 dùng sparse, ngược lại dense.</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr"/>
+      <c r="L43" s="13" t="inlineStr"/>
+      <c r="M43" s="22" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>3R.3</t>
+          <t>2C.1</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Epic 3</t>
+          <t>Epic 2</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>3R Research</t>
+          <t>2C Validation</t>
         </is>
       </c>
       <c r="D44" s="22" t="inlineStr">
         <is>
-          <t>Thiết kế Naive Baseline Detector</t>
+          <t>Unit test invariant Tensor</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -4437,7 +4532,7 @@
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
@@ -4447,52 +4542,52 @@
       </c>
       <c r="I44" s="22" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>2B.1, 2B.2</t>
         </is>
       </c>
       <c r="J44" s="22" t="inlineStr">
         <is>
-          <t>[RESEARCH] Detector đơn giản không MPS (ngưỡng leverage/utilization hoặc graph centrality) làm mốc so sánh chứng minh MPS thêm giá trị (lead-time, false positive) → research/baseline_detector.md. Đủ đơn giản để implement ≤1 story build.</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="n"/>
-      <c r="L44" s="13" t="n"/>
-      <c r="M44" s="22" t="n"/>
+          <t>Viết test suite property-based dùng hypothesis: symmetry adjacency (∀ graph, A == A.T), non-negative feature (tvl, volume ≥ 0), mass conservation (sum flow-in ≈ sum flow-out tolerance 1%). Chạy 500 case random. Fail phải xuất minimal counter-example.</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr"/>
+      <c r="L44" s="13" t="inlineStr"/>
+      <c r="M44" s="22" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>3A.1</t>
+          <t>2C.2</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Epic 3</t>
+          <t>Epic 2</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>3A Baseline</t>
+          <t>2C Validation</t>
         </is>
       </c>
       <c r="D45" s="22" t="inlineStr">
         <is>
-          <t>Contraction naive (torch.einsum)</t>
+          <t>Visualization Heatmap</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 3</t>
+          <t>Quants</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -4502,12 +4597,12 @@
       </c>
       <c r="I45" s="22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2A.3</t>
         </is>
       </c>
       <c r="J45" s="22" t="inlineStr">
         <is>
-          <t>Viết engine/mps/baseline.py: hàm forward_naive(adjacency_tensor) dùng torch.einsum không optimize path. Deterministic (torch.manual_seed(42)). Không dùng GPU. Output là fragility scalar 0-100. Unit test: cùng input → cùng output bit-exact 10 lần chạy.</t>
+          <t>Viết tools/plot_adjacency.py: nhận graph snapshot → sinh heatmap.png (matplotlib) + heatmap_legend.json ghi mapping index→node.id. Config colormap (mặc định viridis). CI job: chạy trên 1 snapshot LUNA, upload artifact.</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr"/>
@@ -4517,37 +4612,37 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>3A.2</t>
+          <t>2C.3</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Epic 3</t>
+          <t>Epic 2</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>3A Baseline</t>
+          <t>2C Validation</t>
         </is>
       </c>
       <c r="D46" s="22" t="inlineStr">
         <is>
-          <t>Harness Pytest-benchmark</t>
+          <t>So sánh với dữ liệu reference</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 3</t>
+          <t>Quants</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -4557,12 +4652,12 @@
       </c>
       <c r="I46" s="22" t="inlineStr">
         <is>
-          <t>3A.1</t>
+          <t>2A.3, 0.4</t>
         </is>
       </c>
       <c r="J46" s="22" t="inlineStr">
         <is>
-          <t>Viết tests/perf/test_mps_bench.py dùng pytest-benchmark: chạy forward_naive 1000 iter, report p50/p95/p99 + std. Sinh HTML report vào .benchmarks/. Cấu hình CI: nếu p95 tệ hơn baseline 10% → fail (compare mode).</t>
+          <t>Lấy top-10 pool theo TVL từ Nansen/Dune public (query id đính kèm) làm reference. So sánh với top-10 edge weight cao nhất sinh từ builder trên cùng thời điểm LUNA t0. AC: ≥ 7/10 pool trùng. Report vào docs/graph_validation.md.</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr"/>
@@ -4572,7 +4667,7 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>3A.3</t>
+          <t>3R.1</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -4582,52 +4677,52 @@
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>3A Baseline</t>
+          <t>3R Research</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>Memory Profiler</t>
+          <t>Đặc tả toán MPS→Fragility (TIÊN QUYẾT)</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 3</t>
+          <t>AI Lead + Quants</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>backlog</t>
+          <t>ready-for-dev</t>
         </is>
       </c>
       <c r="I47" s="22" t="inlineStr">
         <is>
-          <t>3A.2</t>
+          <t>0.2, 2B.1</t>
         </is>
       </c>
       <c r="J47" s="22" t="inlineStr">
         <is>
-          <t>Tích hợp tracemalloc + psutil vào harness: đo peak RSS sau 100 forward pass. Ghi vào bench report. Threshold: fail nếu peak &gt; 500MB. Test: chạy trên graph N=50, N=100, N=200 – confirm không leak (RSS ổn định sau warmup).</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr"/>
-      <c r="L47" s="13" t="inlineStr"/>
-      <c r="M47" s="22" t="inlineStr"/>
+          <t>[RESEARCH][TIÊN QUYẾT] Đặc tả chính thức: adjacency+feature tensor → phân rã MPS/tensor-train → entanglement entropy → Fragility raw. Ký hiệu, chiều tensor, thứ tự contraction, công thức entropy, ánh xạ entropy→Fragility. Kèm ví dụ 3-node tính tay làm test oracle cho 3A.1 → research/mps_fragility_model.md. CHẶN TOÀN BỘ Epic 3.</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n"/>
+      <c r="L47" s="13" t="n"/>
+      <c r="M47" s="22" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>3A.4</t>
+          <t>3R.2</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
@@ -4637,17 +4732,17 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>3A Baseline</t>
+          <t>3R Research</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>Baseline Metrics Report</t>
+          <t>Literature Review Tensor-Network Risk</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 3</t>
+          <t>Quants</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
@@ -4657,7 +4752,7 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
@@ -4667,22 +4762,22 @@
       </c>
       <c r="I48" s="22" t="inlineStr">
         <is>
-          <t>3A.2, 3A.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" s="22" t="inlineStr">
         <is>
-          <t>Sinh docs/metrics/baseline.md gồm: p50/p95/p99 latency (ms), peak RSS (MB), FLOPs estimate. Commit + git tag baseline-v0. Đây là ngưỡng để tracks 3B/3C/3D so sánh và story 3E.1 enable gate 30ms.</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr"/>
-      <c r="L48" s="13" t="inlineStr"/>
-      <c r="M48" s="22" t="inlineStr"/>
+          <t>[RESEARCH] Khảo sát ≥5 nguồn về entanglement entropy làm proxy rủi ro &amp; tensor network trong tài chính. Tóm tắt+trích dẫn+bài học+giả định chưa có tiền lệ → research/literature_review.md.</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="n"/>
+      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="22" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>3B.1</t>
+          <t>3R.3</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
@@ -4692,17 +4787,17 @@
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>3B Bond Dim</t>
+          <t>3R Research</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
-          <t>Runner Bond Dimension sweep</t>
+          <t>Thiết kế Naive Baseline Detector</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 4</t>
+          <t>Quants</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
@@ -4712,7 +4807,7 @@
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
@@ -4722,22 +4817,22 @@
       </c>
       <c r="I49" s="22" t="inlineStr">
         <is>
-          <t>3A.4</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J49" s="22" t="inlineStr">
         <is>
-          <t>Viết tools/sweep_bond_dim.py chạy forward MPS với bond_dim ∈ {8, 16, 32, 64}, đo latency + accuracy vs baseline. Kết quả ghi vào results/bond_sweep.csv. Hỗ trợ --resume để không chạy lại config đã có. Test: chạy full sweep &lt; 15 phút CPU.</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr"/>
-      <c r="L49" s="13" t="inlineStr"/>
-      <c r="M49" s="22" t="inlineStr"/>
+          <t>[RESEARCH] Detector đơn giản không MPS (ngưỡng leverage/utilization hoặc graph centrality) làm mốc so sánh chứng minh MPS thêm giá trị (lead-time, false positive) → research/baseline_detector.md. Đủ đơn giản để implement ≤1 story build.</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="n"/>
+      <c r="L49" s="13" t="n"/>
+      <c r="M49" s="22" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>3B.2</t>
+          <t>3A.1</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
@@ -4747,17 +4842,17 @@
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>3B Bond Dim</t>
+          <t>3A Baseline</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t>Trade-off Matrix Generator</t>
+          <t>Contraction naive (torch.einsum)</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 4</t>
+          <t>AI Engineer 3</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
@@ -4767,7 +4862,7 @@
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
@@ -4777,12 +4872,12 @@
       </c>
       <c r="I50" s="22" t="inlineStr">
         <is>
-          <t>3B.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J50" s="22" t="inlineStr">
         <is>
-          <t>Đọc bond_sweep.csv → tính Pareto front (latency vs accuracy). Weighted recommendation: score = 0.6×(1-latency/baseline) + 0.4×accuracy. Output docs/mps/bond_recommendation.md nêu bond_dim đề xuất + lý do.</t>
+          <t>Viết engine/mps/baseline.py: hàm forward_naive(adjacency_tensor) dùng torch.einsum không optimize path. Deterministic (torch.manual_seed(42)). Không dùng GPU. Output là fragility scalar 0-100. Unit test: cùng input → cùng output bit-exact 10 lần chạy.</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr"/>
@@ -4792,7 +4887,7 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>3B.3</t>
+          <t>3A.2</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
@@ -4802,27 +4897,27 @@
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>3B Bond Dim</t>
+          <t>3A Baseline</t>
         </is>
       </c>
       <c r="D51" s="22" t="inlineStr">
         <is>
-          <t>Visualization Accuracy vs Speed</t>
+          <t>Harness Pytest-benchmark</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 4</t>
+          <t>AI Engineer 3</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">
@@ -4832,12 +4927,12 @@
       </c>
       <c r="I51" s="22" t="inlineStr">
         <is>
-          <t>3B.1</t>
+          <t>3A.1</t>
         </is>
       </c>
       <c r="J51" s="22" t="inlineStr">
         <is>
-          <t>Sinh pareto.png (matplotlib) + pareto_interactive.html (plotly) hover xem chi tiết mỗi config. Deploy vào docs/mps/. CI job attach artifact.</t>
+          <t>Viết tests/perf/test_mps_bench.py dùng pytest-benchmark: chạy forward_naive 1000 iter, report p50/p95/p99 + std. Sinh HTML report vào .benchmarks/. Cấu hình CI: nếu p95 tệ hơn baseline 10% → fail (compare mode).</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr"/>
@@ -4847,7 +4942,7 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>3C.1</t>
+          <t>3A.3</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
@@ -4857,17 +4952,17 @@
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>3C SVD Truncation</t>
+          <t>3A Baseline</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>Wrapper SVD Decomposition</t>
+          <t>Memory Profiler</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 5</t>
+          <t>AI Engineer 3</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
@@ -4887,12 +4982,12 @@
       </c>
       <c r="I52" s="22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3A.2</t>
         </is>
       </c>
       <c r="J52" s="22" t="inlineStr">
         <is>
-          <t>Viết engine/mps/svd.py: hàm truncate(tensor, rank) dùng torch.linalg.svd giữ top-rank singular values. Đo reconstruction error (frobenius). AC: error &lt; 5% cho rank=min(N)/2; benchmark &lt; 3ms cho tensor 50×50.</t>
+          <t>Tích hợp tracemalloc + psutil vào harness: đo peak RSS sau 100 forward pass. Ghi vào bench report. Threshold: fail nếu peak &gt; 500MB. Test: chạy trên graph N=50, N=100, N=200 – confirm không leak (RSS ổn định sau warmup).</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr"/>
@@ -4902,7 +4997,7 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>3C.2</t>
+          <t>3A.4</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
@@ -4912,17 +5007,17 @@
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>3C SVD Truncation</t>
+          <t>3A Baseline</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>Auto-select Truncation Threshold</t>
+          <t>Baseline Metrics Report</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 5</t>
+          <t>AI Engineer 3</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
@@ -4942,12 +5037,12 @@
       </c>
       <c r="I53" s="22" t="inlineStr">
         <is>
-          <t>3C.1</t>
+          <t>3A.2, 3A.3</t>
         </is>
       </c>
       <c r="J53" s="22" t="inlineStr">
         <is>
-          <t>Viết select_rank_by_energy(tensor, threshold=0.95): tự chọn rank nhỏ nhất giữ được 95% năng lượng (cumsum singular values² / total). Test 20 tensor random: verify energy ≥ 0.95 sau truncate.</t>
+          <t>Sinh docs/metrics/baseline.md gồm: p50/p95/p99 latency (ms), peak RSS (MB), FLOPs estimate. Commit + git tag baseline-v0. Đây là ngưỡng để tracks 3B/3C/3D so sánh và story 3E.1 enable gate 30ms.</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr"/>
@@ -4957,7 +5052,7 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>3C.3</t>
+          <t>3B.1</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
@@ -4967,17 +5062,17 @@
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>3C SVD Truncation</t>
+          <t>3B Bond Dim</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Recompression Pipeline</t>
+          <t>Runner Bond Dimension sweep</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 5</t>
+          <t>AI Engineer 4</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
@@ -4987,7 +5082,7 @@
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
@@ -4997,12 +5092,12 @@
       </c>
       <c r="I54" s="22" t="inlineStr">
         <is>
-          <t>3C.1, 3C.2, 3A.4</t>
+          <t>3A.4</t>
         </is>
       </c>
       <c r="J54" s="22" t="inlineStr">
         <is>
-          <t>Tích hợp SVD truncation vào forward pass MPS: sau mỗi contraction step áp truncate với threshold tự chọn. Benchmark so với baseline 3A.4: p95 giảm ≥ 40%, accuracy loss (delta fragility score) &lt; 5%. Report vào docs/mps/svd_impact.md.</t>
+          <t>Viết tools/sweep_bond_dim.py chạy forward MPS với bond_dim ∈ {8, 16, 32, 64}, đo latency + accuracy vs baseline. Kết quả ghi vào results/bond_sweep.csv. Hỗ trợ --resume để không chạy lại config đã có. Test: chạy full sweep &lt; 15 phút CPU.</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr"/>
@@ -5012,7 +5107,7 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>3C.4</t>
+          <t>3B.2</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
@@ -5022,17 +5117,17 @@
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>3C SVD Truncation</t>
+          <t>3B Bond Dim</t>
         </is>
       </c>
       <c r="D55" s="22" t="inlineStr">
         <is>
-          <t>Numerical Stability Guard</t>
+          <t>Trade-off Matrix Generator</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 5</t>
+          <t>AI Engineer 4</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
@@ -5042,7 +5137,7 @@
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">
@@ -5052,12 +5147,12 @@
       </c>
       <c r="I55" s="22" t="inlineStr">
         <is>
-          <t>3C.3</t>
+          <t>3B.1</t>
         </is>
       </c>
       <c r="J55" s="22" t="inlineStr">
         <is>
-          <t>Xử lý rank-deficient (singular value &lt; 1e-10): pad zero, log WARNING kèm tensor shape + condition number. Test với ma trận cố tình singular: không crash, output fragility vẫn ∈ [0, 100].</t>
+          <t>Đọc bond_sweep.csv → tính Pareto front (latency vs accuracy). Weighted recommendation: score = 0.6×(1-latency/baseline) + 0.4×accuracy. Output docs/mps/bond_recommendation.md nêu bond_dim đề xuất + lý do.</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr"/>
@@ -5067,7 +5162,7 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>3D.1</t>
+          <t>3B.3</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
@@ -5077,27 +5172,27 @@
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>3D Kernel Opt</t>
+          <t>3B Bond Dim</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>Path Optimizer với opt_einsum</t>
+          <t>Visualization Accuracy vs Speed</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 6</t>
+          <t>AI Engineer 4</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -5107,12 +5202,12 @@
       </c>
       <c r="I56" s="22" t="inlineStr">
         <is>
-          <t>3A.1</t>
+          <t>3B.1</t>
         </is>
       </c>
       <c r="J56" s="22" t="inlineStr">
         <is>
-          <t>Thay torch.einsum bằng opt_einsum.contract với optimize='dp'. Đo FLOPs giảm bao nhiêu (opt_einsum.contract_path). AC: FLOPs -30% so baseline, latency giảm tương ứng ±10%. Cache path (tensor shape signature → path) để tránh re-plan.</t>
+          <t>Sinh pareto.png (matplotlib) + pareto_interactive.html (plotly) hover xem chi tiết mỗi config. Deploy vào docs/mps/. CI job attach artifact.</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr"/>
@@ -5122,7 +5217,7 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>3D.2</t>
+          <t>3C.1</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
@@ -5132,27 +5227,27 @@
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>3D Kernel Opt</t>
+          <t>3C SVD Truncation</t>
         </is>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
-          <t>TorchScript Compilation</t>
+          <t>Wrapper SVD Decomposition</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 6</t>
+          <t>AI Engineer 5</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
@@ -5162,12 +5257,12 @@
       </c>
       <c r="I57" s="22" t="inlineStr">
         <is>
-          <t>3A.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J57" s="22" t="inlineStr">
         <is>
-          <t>Torch.jit.script forward function. Benchmark: p95 giảm ≥ 15% so với eager. Output tolerance vs eager: 1e-6 (nới từ bit-identical vì TS có drift). Fallback nếu compile fail → eager mode + log.</t>
+          <t>Viết engine/mps/svd.py: hàm truncate(tensor, rank) dùng torch.linalg.svd giữ top-rank singular values. Đo reconstruction error (frobenius). AC: error &lt; 5% cho rank=min(N)/2; benchmark &lt; 3ms cho tensor 50×50.</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr"/>
@@ -5177,7 +5272,7 @@
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>3D.3</t>
+          <t>3C.2</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
@@ -5187,27 +5282,27 @@
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>3D Kernel Opt</t>
+          <t>3C SVD Truncation</t>
         </is>
       </c>
       <c r="D58" s="22" t="inlineStr">
         <is>
-          <t>Tensor Reuse &amp; Cache Warmup</t>
+          <t>Auto-select Truncation Threshold</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>AI Engineer 6</t>
+          <t>AI Engineer 5</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
@@ -5217,12 +5312,12 @@
       </c>
       <c r="I58" s="22" t="inlineStr">
         <is>
-          <t>3A.1</t>
+          <t>3C.1</t>
         </is>
       </c>
       <c r="J58" s="22" t="inlineStr">
         <is>
-          <t>Pre-allocate buffer tensor tái sử dụng qua các forward pass (torch.empty reuse). Warmup 10 iter khi startup. Đo allocation count via torch.cuda.memory_stats trên CPU tương đương: giảm ≥ 50%; verify RSS không tăng theo thời gian (leak-free).</t>
+          <t>Viết select_rank_by_energy(tensor, threshold=0.95): tự chọn rank nhỏ nhất giữ được 95% năng lượng (cumsum singular values² / total). Test 20 tensor random: verify energy ≥ 0.95 sau truncate.</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr"/>
@@ -5232,7 +5327,7 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>3E.1</t>
+          <t>3C.3</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
@@ -5242,17 +5337,17 @@
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>3E E2E Gate</t>
+          <t>3C SVD Truncation</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>Gate: MPS Forward Pass &lt; 30ms</t>
+          <t>Recompression Pipeline</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>AI Lead</t>
+          <t>AI Engineer 5</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
@@ -5262,7 +5357,7 @@
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
@@ -5272,12 +5367,12 @@
       </c>
       <c r="I59" s="22" t="inlineStr">
         <is>
-          <t>3B.2, 3C.4, 3D.3</t>
+          <t>3C.1, 3C.2, 3A.4</t>
         </is>
       </c>
       <c r="J59" s="22" t="inlineStr">
         <is>
-          <t>Enable CI gate: chạy forward pipeline (2B → 3B config chọn → 3C + 3D optimize), fail nếu p95 &gt; 30ms trên graph N=50. Chỉ enable sau khi 3A.4 baseline commit. Ghi threshold vào .github/workflows/perf-gate.yml.</t>
+          <t>Tích hợp SVD truncation vào forward pass MPS: sau mỗi contraction step áp truncate với threshold tự chọn. Benchmark so với baseline 3A.4: p95 giảm ≥ 40%, accuracy loss (delta fragility score) &lt; 5%. Report vào docs/mps/svd_impact.md.</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr"/>
@@ -5287,7 +5382,7 @@
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>3E.2</t>
+          <t>3C.4</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
@@ -5297,17 +5392,17 @@
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>3E E2E Gate</t>
+          <t>3C SVD Truncation</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>Numerical Stability Guard</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>AI Lead</t>
+          <t>AI Engineer 5</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
@@ -5317,7 +5412,7 @@
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -5327,12 +5422,12 @@
       </c>
       <c r="I60" s="22" t="inlineStr">
         <is>
-          <t>3E.1</t>
+          <t>3C.3</t>
         </is>
       </c>
       <c r="J60" s="22" t="inlineStr">
         <is>
-          <t>Bộ 20 fixture graph (đa dạng size N=10..200) → chạy full MPS pipeline → verify output nằm trong tolerance so với snapshot (regression file). Bảo vệ khỏi drift. Ghi docs/mps/optimized.md, git tag mps-optimized-v1.</t>
+          <t>Xử lý rank-deficient (singular value &lt; 1e-10): pad zero, log WARNING kèm tensor shape + condition number. Test với ma trận cố tình singular: không crash, output fragility vẫn ∈ [0, 100].</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr"/>
@@ -5342,92 +5437,92 @@
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>4R.1</t>
+          <t>3D.1</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>Epic 4</t>
+          <t>Epic 3</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>4R Research</t>
+          <t>3D Kernel Opt</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Latency Budget E2E (&lt;50ms)</t>
+          <t>Path Optimizer với opt_einsum</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>AI Engineer 6</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
-          <t>ready-for-dev</t>
+          <t>backlog</t>
         </is>
       </c>
       <c r="I61" s="22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3A.1</t>
         </is>
       </c>
       <c r="J61" s="22" t="inlineStr">
         <is>
-          <t>[RESEARCH] Phân bổ NFR1 &lt;50ms cho từng stage (WS→decode→buffer→graph→tensor→MPS→payload→webhook), tổng ≤50ms + buffer → research/latency_budget.md. Thành target cho gate 3E.1/5.3/6.1. CHẶN mọi perf gate.</t>
-        </is>
-      </c>
-      <c r="K61" s="13" t="n"/>
-      <c r="L61" s="13" t="n"/>
-      <c r="M61" s="22" t="n"/>
+          <t>Thay torch.einsum bằng opt_einsum.contract với optimize='dp'. Đo FLOPs giảm bao nhiêu (opt_einsum.contract_path). AC: FLOPs -30% so baseline, latency giảm tương ứng ±10%. Cache path (tensor shape signature → path) để tránh re-plan.</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr"/>
+      <c r="L61" s="13" t="inlineStr"/>
+      <c r="M61" s="22" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>4R.2</t>
+          <t>3D.2</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>Epic 4</t>
+          <t>Epic 3</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>4R Research</t>
+          <t>3D Kernel Opt</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t>IPC Spike (SharedMemory/Queue/Pipe)</t>
+          <t>TorchScript Compilation</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>AI Engineer 6</t>
         </is>
       </c>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -5437,52 +5532,52 @@
       </c>
       <c r="I62" s="22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3A.1</t>
         </is>
       </c>
       <c r="J62" s="22" t="inlineStr">
         <is>
-          <t>[RESEARCH] Benchmark overhead serialize tensor/graph qua SharedMemory vs Queue vs Pipe cho main↔engine → research/ipc_decision.md. Khớp latency budget 4R.1. CHẶN 4.3.</t>
-        </is>
-      </c>
-      <c r="K62" s="13" t="n"/>
-      <c r="L62" s="13" t="n"/>
-      <c r="M62" s="22" t="n"/>
+          <t>Torch.jit.script forward function. Benchmark: p95 giảm ≥ 15% so với eager. Output tolerance vs eager: 1e-6 (nới từ bit-identical vì TS có drift). Fallback nếu compile fail → eager mode + log.</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr"/>
+      <c r="L62" s="13" t="inlineStr"/>
+      <c r="M62" s="22" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>4R.3</t>
+          <t>3D.3</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>Epic 4</t>
+          <t>Epic 3</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>4R Research</t>
+          <t>3D Kernel Opt</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Failure Mode &amp; Recovery (FMEA)</t>
+          <t>Tensor Reuse &amp; Cache Warmup</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>AI Engineer 6</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
@@ -5492,42 +5587,42 @@
       </c>
       <c r="I63" s="22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3A.1</t>
         </is>
       </c>
       <c r="J63" s="22" t="inlineStr">
         <is>
-          <t>[RESEARCH] FMEA: WS đứt, engine crash, queue overflow, data malformed, webhook timeout — mỗi mode (nguyên nhân, phát hiện, hành vi kỳ vọng, recovery) → research/failure_modes.md. Map mỗi mode tới story build (1A.3, 4.4...).</t>
-        </is>
-      </c>
-      <c r="K63" s="13" t="n"/>
-      <c r="L63" s="13" t="n"/>
-      <c r="M63" s="22" t="n"/>
+          <t>Pre-allocate buffer tensor tái sử dụng qua các forward pass (torch.empty reuse). Warmup 10 iter khi startup. Đo allocation count via torch.cuda.memory_stats trên CPU tương đương: giảm ≥ 50%; verify RSS không tăng theo thời gian (leak-free).</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr"/>
+      <c r="L63" s="13" t="inlineStr"/>
+      <c r="M63" s="22" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>4R.4</t>
+          <t>3E.1</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>Epic 4</t>
+          <t>Epic 3</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>4R Research</t>
+          <t>3E E2E Gate</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Sơ đồ Data-Flow toàn hệ thống</t>
+          <t>Gate: MPS Forward Pass &lt; 30ms</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>AI Lead</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
@@ -5537,7 +5632,7 @@
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
@@ -5547,47 +5642,47 @@
       </c>
       <c r="I64" s="22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3B.2, 3C.4, 3D.3</t>
         </is>
       </c>
       <c r="J64" s="22" t="inlineStr">
         <is>
-          <t>[RESEARCH] Diagram mermaid toàn pipeline + kiểu dữ liệu mỗi ranh giới (TickDataEvent, GraphSnapshot, tensor, FragilityPayload), đánh dấu ranh giới process (asyncio main vs engine) → docs/data_flow.md.</t>
-        </is>
-      </c>
-      <c r="K64" s="13" t="n"/>
-      <c r="L64" s="13" t="n"/>
-      <c r="M64" s="22" t="n"/>
+          <t>Enable CI gate: chạy forward pipeline (2B → 3B config chọn → 3C + 3D optimize), fail nếu p95 &gt; 30ms trên graph N=50. Chỉ enable sau khi 3A.4 baseline commit. Ghi threshold vào .github/workflows/perf-gate.yml.</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr"/>
+      <c r="L64" s="13" t="inlineStr"/>
+      <c r="M64" s="22" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3E.2</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>Epic 4</t>
+          <t>Epic 3</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>3E E2E Gate</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Calibrate Fragility trên LUNA/UST</t>
+          <t>Regression Suite</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>Risk Manager + Quants</t>
+          <t>AI Lead</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
@@ -5602,12 +5697,12 @@
       </c>
       <c r="I65" s="22" t="inlineStr">
         <is>
-          <t>3E.2, 1D.3</t>
+          <t>3E.1</t>
         </is>
       </c>
       <c r="J65" s="22" t="inlineStr">
         <is>
-          <t>Replay fixture LUNA (0.4) qua pipeline. Tune tham số sigmoid / threshold sao cho: (a) alert RED (score ≥ 90) fire ≥ 10 phút trước block liquidation đầu tiên (2022-05-09 03:34 UTC), (b) false positive trong 7 ngày control &lt; 5%. Ghi tham số cuối vào config/fragility_params.yaml + docs/calibration_luna.md kèm biểu đồ score theo time.</t>
+          <t>Bộ 20 fixture graph (đa dạng size N=10..200) → chạy full MPS pipeline → verify output nằm trong tolerance so với snapshot (regression file). Bảo vệ khỏi drift. Ghi docs/mps/optimized.md, git tag mps-optimized-v1.</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr"/>
@@ -5617,7 +5712,7 @@
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4R.1</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
@@ -5627,17 +5722,17 @@
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>4R Research</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Cross-validate với FTX</t>
+          <t>Latency Budget E2E (&lt;50ms)</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>Risk Manager</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
@@ -5647,32 +5742,32 @@
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>backlog</t>
+          <t>ready-for-dev</t>
         </is>
       </c>
       <c r="I66" s="22" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J66" s="22" t="inlineStr">
         <is>
-          <t>Dùng CHÍNH XÁC tham số từ 4.1 (không tune lại), replay fixture FTX. AC: RED fire ≥ 10 phút trước block liquidation FTX chain, FP &lt; 5%. Nếu fail → phân tích khác biệt và document (không được đổi tham số riêng cho FTX).</t>
-        </is>
-      </c>
-      <c r="K66" s="13" t="inlineStr"/>
-      <c r="L66" s="13" t="inlineStr"/>
-      <c r="M66" s="22" t="inlineStr"/>
+          <t>[RESEARCH] Phân bổ NFR1 &lt;50ms cho từng stage (WS→decode→buffer→graph→tensor→MPS→payload→webhook), tổng ≤50ms + buffer → research/latency_budget.md. Thành target cho gate 3E.1/5.3/6.1. CHẶN mọi perf gate.</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="n"/>
+      <c r="L66" s="13" t="n"/>
+      <c r="M66" s="22" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4R.2</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
@@ -5682,17 +5777,17 @@
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>4R Research</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Multiprocessing Wrapper cho MPS Engine</t>
+          <t>IPC Spike (SharedMemory/Queue/Pipe)</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
@@ -5702,7 +5797,7 @@
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
@@ -5712,22 +5807,22 @@
       </c>
       <c r="I67" s="22" t="inlineStr">
         <is>
-          <t>3E.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J67" s="22" t="inlineStr">
         <is>
-          <t>Chạy MPS forward trong multiprocessing.Process riêng, giao tiếp qua multiprocessing.Queue hoặc SharedMemory. Verify PID khác main. Main loop chỉ đợi result async, response time &lt; 5ms khi engine đang bận. Test: kill engine PID → main tự restart engine trong 2s.</t>
-        </is>
-      </c>
-      <c r="K67" s="13" t="inlineStr"/>
-      <c r="L67" s="13" t="inlineStr"/>
-      <c r="M67" s="22" t="inlineStr"/>
+          <t>[RESEARCH] Benchmark overhead serialize tensor/graph qua SharedMemory vs Queue vs Pipe cho main↔engine → research/ipc_decision.md. Khớp latency budget 4R.1. CHẶN 4.3.</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="n"/>
+      <c r="L67" s="13" t="n"/>
+      <c r="M67" s="22" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4R.3</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
@@ -5737,27 +5832,27 @@
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>4R Research</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>Backpressure &amp; Circuit Breaker (confirm scope)</t>
+          <t>Failure Mode &amp; Recovery (FMEA)</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -5767,42 +5862,42 @@
       </c>
       <c r="I68" s="22" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J68" s="22" t="inlineStr">
         <is>
-          <t>Nếu queue MPS ≥ 80% capacity → drop frame cũ nhất, log WARNING. Circuit breaker: nếu 3 forward liên tiếp &gt; 100ms → mở circuit 30s (skip forward, giữ score cũ). Verify p99 latency &lt; 60ms dưới load 2x throughput. LƯU Ý: story này ngoài SPEC gốc, confirm với PM trước Sprint 6.</t>
-        </is>
-      </c>
-      <c r="K68" s="13" t="inlineStr"/>
-      <c r="L68" s="13" t="inlineStr"/>
-      <c r="M68" s="22" t="inlineStr"/>
+          <t>[RESEARCH] FMEA: WS đứt, engine crash, queue overflow, data malformed, webhook timeout — mỗi mode (nguyên nhân, phát hiện, hành vi kỳ vọng, recovery) → research/failure_modes.md. Map mỗi mode tới story build (1A.3, 4.4...).</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="n"/>
+      <c r="L68" s="13" t="n"/>
+      <c r="M68" s="22" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4R.4</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>Epic 5</t>
+          <t>Epic 4</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
-          <t>API/Emitter</t>
+          <t>4R Research</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>FastAPI Subscribe/Unsubscribe</t>
+          <t>Sơ đồ Data-Flow toàn hệ thống</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
@@ -5822,52 +5917,52 @@
       </c>
       <c r="I69" s="22" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J69" s="22" t="inlineStr">
         <is>
-          <t>Viết emitter/api.py: POST /subscribe {webhook_url, filter?} → trả subscription_id UUID, persist vào file JSON (data/subscriptions.json). DELETE /subscribe/{id} → remove. GET /subscribe → list. Test integration TestClient: subscribe 3 URL, list = 3, delete 1, còn 2. Persist qua restart.</t>
-        </is>
-      </c>
-      <c r="K69" s="13" t="inlineStr"/>
-      <c r="L69" s="13" t="inlineStr"/>
-      <c r="M69" s="22" t="inlineStr"/>
+          <t>[RESEARCH] Diagram mermaid toàn pipeline + kiểu dữ liệu mỗi ranh giới (TickDataEvent, GraphSnapshot, tensor, FragilityPayload), đánh dấu ranh giới process (asyncio main vs engine) → docs/data_flow.md.</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="n"/>
+      <c r="L69" s="13" t="n"/>
+      <c r="M69" s="22" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>Epic 5</t>
+          <t>Epic 4</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>API/Emitter</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>Formatter JSON Payload</t>
+          <t>Calibrate Fragility trên LUNA/UST</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Risk Manager + Quants</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
@@ -5877,12 +5972,12 @@
       </c>
       <c r="I70" s="22" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3E.2, 1D.3</t>
         </is>
       </c>
       <c r="J70" s="22" t="inlineStr">
         <is>
-          <t>Viết emitter/formatter.py: build_payload(fragility_score, trigger_protocols) → dict tuân schema 0.3. Logic alert_level: score ≥ 90 → 'red', 70 ≤ score &lt; 90 → 'yellow', &lt; 70 → không emit. Timestamp ISO 8601 UTC (kết Z). Test: 3 case score, output pass schema validate.</t>
+          <t>Replay fixture LUNA (0.4) qua pipeline. Tune tham số sigmoid / threshold sao cho: (a) alert RED (score ≥ 90) fire ≥ 10 phút trước block liquidation đầu tiên (2022-05-09 03:34 UTC), (b) false positive trong 7 ngày control &lt; 5%. Ghi tham số cuối vào config/fragility_params.yaml + docs/calibration_luna.md kèm biểu đồ score theo time.</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr"/>
@@ -5892,37 +5987,37 @@
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>Epic 5</t>
+          <t>Epic 4</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>API/Emitter</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="D71" s="22" t="inlineStr">
         <is>
-          <t>Async Webhook Emitter</t>
+          <t>Cross-validate với FTX</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Risk Manager</t>
         </is>
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
@@ -5932,12 +6027,12 @@
       </c>
       <c r="I71" s="22" t="inlineStr">
         <is>
-          <t>5.1, 5.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="J71" s="22" t="inlineStr">
         <is>
-          <t>Viết emitter/webhook.py dùng aiohttp: fan-out payload tới tất cả subscription song song với asyncio.gather. Timeout 5s/URL. Retry 1 lần khi lỗi mạng. Fail cuối → log ERROR + counter webhook_failures_total. Test: 5 subscription, 1 URL trả 500 → 4 success, 1 log error, không block.</t>
+          <t>Dùng CHÍNH XÁC tham số từ 4.1 (không tune lại), replay fixture FTX. AC: RED fire ≥ 10 phút trước block liquidation FTX chain, FP &lt; 5%. Nếu fail → phân tích khác biệt và document (không được đổi tham số riêng cho FTX).</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr"/>
@@ -5947,37 +6042,37 @@
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>Epic 5</t>
+          <t>Epic 4</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>API/Emitter</t>
+          <t>Isolation</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>API Authentication (confirm scope)</t>
+          <t>Multiprocessing Wrapper cho MPS Engine</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -5987,12 +6082,12 @@
       </c>
       <c r="I72" s="22" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3E.2</t>
         </is>
       </c>
       <c r="J72" s="22" t="inlineStr">
         <is>
-          <t>Bảo vệ /subscribe bằng header X-API-Key (env API_KEYS list). Rate limit 100 req/min/key dùng slowapi. Test: no key → 401, key sai → 403, quá limit → 429. LƯU Ý: SPEC gốc chưa yêu cầu, confirm scope trước khi làm.</t>
+          <t>Chạy MPS forward trong multiprocessing.Process riêng, giao tiếp qua multiprocessing.Queue hoặc SharedMemory. Verify PID khác main. Main loop chỉ đợi result async, response time &lt; 5ms khi engine đang bận. Test: kill engine PID → main tự restart engine trong 2s.</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr"/>
@@ -6002,32 +6097,32 @@
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>Epic 6</t>
+          <t>Epic 4</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>E2E Verify</t>
+          <t>Isolation</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Benchmark E2E Latency (NFR1)</t>
+          <t>Backpressure &amp; Circuit Breaker (confirm scope)</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
@@ -6042,12 +6137,12 @@
       </c>
       <c r="I73" s="22" t="inlineStr">
         <is>
-          <t>1E.1, 4.3, 5.3</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="J73" s="22" t="inlineStr">
         <is>
-          <t>Viết tests/e2e/test_latency.py: chạy pipeline đầy đủ (WS → decode → buffer → MPS → webhook receiver mock) trên 10.000 block replay. Đo delta từ block.received_ts đến webhook.sent_ts. AC: p95 &lt; 50ms, p99 &lt; 80ms. Report HTML lưu vào .benchmarks/e2e/.</t>
+          <t>Nếu queue MPS ≥ 80% capacity → drop frame cũ nhất, log WARNING. Circuit breaker: nếu 3 forward liên tiếp &gt; 100ms → mở circuit 30s (skip forward, giữ score cũ). Verify p99 latency &lt; 60ms dưới load 2x throughput. LƯU Ý: story này ngoài SPEC gốc, confirm với PM trước Sprint 6.</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr"/>
@@ -6057,27 +6152,27 @@
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>Epic 6</t>
+          <t>Epic 5</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>E2E Verify</t>
+          <t>API/Emitter</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Verify No-GPU Runtime (NFR5)</t>
+          <t>FastAPI Subscribe/Unsubscribe</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
@@ -6087,7 +6182,7 @@
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
@@ -6097,12 +6192,12 @@
       </c>
       <c r="I74" s="22" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J74" s="22" t="inlineStr">
         <is>
-          <t>Thêm CI matrix job runs-on: ubuntu-latest với CUDA disabled (torch.cuda.is_available() = False assert). Chạy full test suite. Verify output MPS forward khớp GPU-off vs GPU-on (nếu có) tolerance 1e-6. Docker image production không cài CUDA runtime (verify size).</t>
+          <t>Viết emitter/api.py: POST /subscribe {webhook_url, filter?} → trả subscription_id UUID, persist vào file JSON (data/subscriptions.json). DELETE /subscribe/{id} → remove. GET /subscribe → list. Test integration TestClient: subscribe 3 URL, list = 3, delete 1, còn 2. Persist qua restart.</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr"/>
@@ -6112,37 +6207,37 @@
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>Epic 6</t>
+          <t>Epic 5</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>E2E Verify</t>
+          <t>API/Emitter</t>
         </is>
       </c>
       <c r="D75" s="22" t="inlineStr">
         <is>
-          <t>Bằng chứng Success Signal cuối cùng</t>
+          <t>Formatter JSON Payload</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>PM + SRE</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H75" s="13" t="inlineStr">
@@ -6152,17 +6247,292 @@
       </c>
       <c r="I75" s="22" t="inlineStr">
         <is>
-          <t>4.1, 4.2, 6.1</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J75" s="22" t="inlineStr">
         <is>
-          <t>Chạy demo end-to-end trên fixture LUNA và FTX, quay screencast (asciinema/OBS) show: (a) pipeline start, (b) fragility score tăng dần, (c) RED alert fire ≥ 10 phút trước block liquidation, (d) webhook nhận payload đúng schema. Commit vào docs/demo/ + link vào README. Đây là bằng chứng SPEC Success Signal.</t>
+          <t>Viết emitter/formatter.py: build_payload(fragility_score, trigger_protocols) → dict tuân schema 0.3. Logic alert_level: score ≥ 90 → 'red', 70 ≤ score &lt; 90 → 'yellow', &lt; 70 → không emit. Timestamp ISO 8601 UTC (kết Z). Test: 3 case score, output pass schema validate.</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr"/>
       <c r="L75" s="13" t="inlineStr"/>
       <c r="M75" s="22" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>Epic 5</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>API/Emitter</t>
+        </is>
+      </c>
+      <c r="D76" s="22" t="inlineStr">
+        <is>
+          <t>Async Webhook Emitter</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="F76" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H76" s="13" t="inlineStr">
+        <is>
+          <t>backlog</t>
+        </is>
+      </c>
+      <c r="I76" s="22" t="inlineStr">
+        <is>
+          <t>5.1, 5.2</t>
+        </is>
+      </c>
+      <c r="J76" s="22" t="inlineStr">
+        <is>
+          <t>Viết emitter/webhook.py dùng aiohttp: fan-out payload tới tất cả subscription song song với asyncio.gather. Timeout 5s/URL. Retry 1 lần khi lỗi mạng. Fail cuối → log ERROR + counter webhook_failures_total. Test: 5 subscription, 1 URL trả 500 → 4 success, 1 log error, không block.</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="inlineStr"/>
+      <c r="L76" s="13" t="inlineStr"/>
+      <c r="M76" s="22" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>Epic 5</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>API/Emitter</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="inlineStr">
+        <is>
+          <t>API Authentication (confirm scope)</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H77" s="13" t="inlineStr">
+        <is>
+          <t>backlog</t>
+        </is>
+      </c>
+      <c r="I77" s="22" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="J77" s="22" t="inlineStr">
+        <is>
+          <t>Bảo vệ /subscribe bằng header X-API-Key (env API_KEYS list). Rate limit 100 req/min/key dùng slowapi. Test: no key → 401, key sai → 403, quá limit → 429. LƯU Ý: SPEC gốc chưa yêu cầu, confirm scope trước khi làm.</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="inlineStr"/>
+      <c r="L77" s="13" t="inlineStr"/>
+      <c r="M77" s="22" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>E2E Verify</t>
+        </is>
+      </c>
+      <c r="D78" s="22" t="inlineStr">
+        <is>
+          <t>Benchmark E2E Latency (NFR1)</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>SRE</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="H78" s="13" t="inlineStr">
+        <is>
+          <t>backlog</t>
+        </is>
+      </c>
+      <c r="I78" s="22" t="inlineStr">
+        <is>
+          <t>1E.1, 4.3, 5.3</t>
+        </is>
+      </c>
+      <c r="J78" s="22" t="inlineStr">
+        <is>
+          <t>Viết tests/e2e/test_latency.py: chạy pipeline đầy đủ (WS → decode → buffer → MPS → webhook receiver mock) trên 10.000 block replay. Đo delta từ block.received_ts đến webhook.sent_ts. AC: p95 &lt; 50ms, p99 &lt; 80ms. Report HTML lưu vào .benchmarks/e2e/.</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="inlineStr"/>
+      <c r="L78" s="13" t="inlineStr"/>
+      <c r="M78" s="22" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>E2E Verify</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="inlineStr">
+        <is>
+          <t>Verify No-GPU Runtime (NFR5)</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>SRE</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G79" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="H79" s="13" t="inlineStr">
+        <is>
+          <t>backlog</t>
+        </is>
+      </c>
+      <c r="I79" s="22" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="J79" s="22" t="inlineStr">
+        <is>
+          <t>Thêm CI matrix job runs-on: ubuntu-latest với CUDA disabled (torch.cuda.is_available() = False assert). Chạy full test suite. Verify output MPS forward khớp GPU-off vs GPU-on (nếu có) tolerance 1e-6. Docker image production không cài CUDA runtime (verify size).</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="inlineStr"/>
+      <c r="L79" s="13" t="inlineStr"/>
+      <c r="M79" s="22" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>E2E Verify</t>
+        </is>
+      </c>
+      <c r="D80" s="22" t="inlineStr">
+        <is>
+          <t>Bằng chứng Success Signal cuối cùng</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>PM + SRE</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G80" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="H80" s="13" t="inlineStr">
+        <is>
+          <t>backlog</t>
+        </is>
+      </c>
+      <c r="I80" s="22" t="inlineStr">
+        <is>
+          <t>4.1, 4.2, 6.1</t>
+        </is>
+      </c>
+      <c r="J80" s="22" t="inlineStr">
+        <is>
+          <t>Chạy demo end-to-end trên fixture LUNA và FTX, quay screencast (asciinema/OBS) show: (a) pipeline start, (b) fragility score tăng dần, (c) RED alert fire ≥ 10 phút trước block liquidation, (d) webhook nhận payload đúng schema. Commit vào docs/demo/ + link vào README. Đây là bằng chứng SPEC Success Signal.</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="inlineStr"/>
+      <c r="L80" s="13" t="inlineStr"/>
+      <c r="M80" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:M63">
@@ -6194,13 +6564,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="H2:H75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"backlog,ready-for-dev,in-progress,review,done,blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sprint 1,Sprint 2,Sprint 3,Sprint 4,Sprint 5,Sprint 6"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6214,7 +6584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6299,57 +6669,57 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Epic 1</t>
+          <t>Epic E</t>
         </is>
       </c>
       <c r="B3" s="22" t="inlineStr">
         <is>
-          <t>Data Ingestion &amp; State</t>
+          <t>Environment &amp; Config Provisioning</t>
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D3" s="22" t="inlineStr">
         <is>
-          <t>FR1, FR2</t>
+          <t>Enables FR1 (WSS), FR2 (contracts), FR4 (webhook)</t>
         </is>
       </c>
       <c r="E3" s="13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2-4</t>
+          <t>Sprint 1</t>
         </is>
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t>5 tracks: 1A/1B/1C/1D/1E; +Track 1R (data research)</t>
+          <t>[SETUP]: E.1-E.3 config/ops, E.4 check_env script, E.5 usage+git docs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>Epic 2</t>
+          <t>Epic 1</t>
         </is>
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>Tensor Graph Modeling</t>
+          <t>Data Ingestion &amp; State</t>
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D4" s="22" t="inlineStr">
         <is>
-          <t>FR3 representation</t>
+          <t>FR1, FR2</t>
         </is>
       </c>
       <c r="E4" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
@@ -6358,126 +6728,126 @@
       </c>
       <c r="G4" s="22" t="inlineStr">
         <is>
-          <t>3 tracks: 2A/2B/2C; +Track 2R (model input)</t>
+          <t>5 tracks: 1A/1B/1C/1D/1E; +Track 1R (data research)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Epic 3</t>
+          <t>Epic 2</t>
         </is>
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>MPS Algorithm Optimization</t>
+          <t>Tensor Graph Modeling</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>FR3 computation</t>
+          <t>FR3 representation</t>
         </is>
       </c>
       <c r="E5" s="13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2-5</t>
+          <t>Sprint 2-4</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t>5 tracks: 3A/3B/3C/3D/3E; +Track 3R (math, PREREQ)</t>
+          <t>3 tracks: 2A/2B/2C; +Track 2R (model input)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>Epic 4</t>
+          <t>Epic 3</t>
         </is>
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>Risk Calibration &amp; Isolation</t>
+          <t>MPS Algorithm Optimization</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>FR3 calibration + Success Signal</t>
+          <t>FR3 computation</t>
         </is>
       </c>
       <c r="E6" s="13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Sprint 5-6</t>
+          <t>Sprint 2-5</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t>Cần Epic 3E xong; +4R arch/latency design</t>
+          <t>5 tracks: 3A/3B/3C/3D/3E; +Track 3R (math, PREREQ)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Epic 5</t>
+          <t>Epic 4</t>
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>Alert System &amp; API</t>
+          <t>Risk Calibration &amp; Isolation</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>FR4, FR5</t>
+          <t>FR3 calibration + Success Signal</t>
         </is>
       </c>
       <c r="E7" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Sprint 2-4</t>
+          <t>Sprint 5-6</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>Song song từ Sprint 2 (dùng mock)</t>
+          <t>Cần Epic 3E xong; +4R arch/latency design</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Epic 6</t>
+          <t>Epic 5</t>
         </is>
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>E2E Verification &amp; NFR Audit</t>
+          <t>Alert System &amp; API</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>NFR1, NFR5, Success Signal</t>
+          <t>FR4, FR5</t>
         </is>
       </c>
       <c r="E8" s="13" t="n">
@@ -6485,10 +6855,43 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
+          <t>Sprint 2-4</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Song song từ Sprint 2 (dùng mock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>E2E Verification &amp; NFR Audit</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>NFR1, NFR5, Success Signal</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>Final gate</t>
         </is>
@@ -8007,4 +8410,937 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>QuantumRadar — Onboarding cho người mới (nguồn: Story E.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="33" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="C2" s="33" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D2" s="33" t="inlineStr">
+        <is>
+          <t>Lệnh / Tham chiếu</t>
+        </is>
+      </c>
+      <c r="E2" s="33" t="inlineStr">
+        <is>
+          <t>Xong?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t>Cài Python 3.11+ và git</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>python3 --version  •  git --version</t>
+        </is>
+      </c>
+      <c r="E3" s="34" t="inlineStr"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Clone repo</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>git clone &lt;repo-url&gt; quantumradar &amp;&amp; cd quantumradar</t>
+        </is>
+      </c>
+      <c r="E4" s="34" t="inlineStr"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Tạo .env từ template (local: dùng mock, không cần key)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>cp .env.example .env  → set WSS_URL=ws://localhost:8546</t>
+        </is>
+      </c>
+      <c r="E5" s="34" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Tạo virtualenv + cài deps</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>python3 -m venv .venv &amp;&amp; source .venv/bin/activate &amp;&amp; pip install -e ".[dev]"</t>
+        </is>
+      </c>
+      <c r="E6" s="34" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>Chạy mock WebSocket server (terminal 1)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>python3 -m tools.mock_wss --scenario luna --speed asap</t>
+        </is>
+      </c>
+      <c r="E7" s="36" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Chạy pipeline realtime với mock (terminal 2)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>python3 -m ingestion.pipeline --source mock   (Ctrl-C để dừng)</t>
+        </is>
+      </c>
+      <c r="E8" s="36" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Chạy backtest replay (không cần server/key)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>python3 -m ingestion.pipeline --source backtest --scenario luna --speed 100x</t>
+        </is>
+      </c>
+      <c r="E9" s="36" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Xem Prometheus metrics</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>curl http://127.0.0.1:9090/metrics</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Chạy toàn bộ test</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>python3 -m pytest</t>
+        </is>
+      </c>
+      <c r="E11" s="38" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Chạy test theo keyword</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>python3 -m pytest -k router</t>
+        </is>
+      </c>
+      <c r="E12" s="38" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>Git</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Đặt danh tính git (1 lần)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>git config --global user.name / user.email</t>
+        </is>
+      </c>
+      <c r="E13" s="40" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>Git</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Đọc quy ước &amp; lệnh git</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>docs/git_workflow.md</t>
+        </is>
+      </c>
+      <c r="E14" s="40" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>Git</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Tạo nhánh làm việc (feat/ | fix/ | chore/)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>git switch -c feat/my-task</t>
+        </is>
+      </c>
+      <c r="E15" s="40" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>Git</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Commit theo Conventional Commits</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>git add &lt;file&gt; &amp;&amp; git commit -m "feat: ..."</t>
+        </is>
+      </c>
+      <c r="E16" s="40" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>Git</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Đẩy nhánh + mở PR vào main</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>git push -u origin feat/my-task</t>
+        </is>
+      </c>
+      <c r="E17" s="40" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>Git</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Kiểm .env KHÔNG bị commit</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>git check-ignore .env   → phải in .env</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="42" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Đọc hướng dẫn đầy đủ</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>docs/usage_guide.md</t>
+        </is>
+      </c>
+      <c r="E19" s="42" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Lấy API key thật (khi cần mainnet)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>docs/environment_setup.md (Story E.1)</t>
+        </is>
+      </c>
+      <c r="E20" s="42" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="42" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>Đọc checklist đóng góp</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>CONTRIBUTING.md</t>
+        </is>
+      </c>
+      <c r="E21" s="42" t="inlineStr"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>GitHub — Hướng dẫn chi tiết A-Z (lần đầu dùng GitHub)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>Bước</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>Thao tác / Lệnh (+ ghi chú)</t>
+        </is>
+      </c>
+      <c r="E24" s="33" t="inlineStr">
+        <is>
+          <t>Xong?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>Chung</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Tạo tài khoản GitHub</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>Vào https://github.com/signup — xác minh email. Nhớ USERNAME + email đã dùng.</t>
+        </is>
+      </c>
+      <c r="E25" s="45" t="inlineStr"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="46" t="inlineStr">
+        <is>
+          <t>Chung</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>Cài Git</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>macOS: brew install git  •  Windows: https://git-scm.com  → kiểm: git --version</t>
+        </is>
+      </c>
+      <c r="E26" s="45" t="inlineStr"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>Chung</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>Cấu hình danh tính git</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>git config --global user.name "Tên"  &amp;&amp;  git config --global user.email "email-GitHub"  (email PHẢI trùng email GitHub để commit gắn đúng tài khoản)</t>
+        </is>
+      </c>
+      <c r="E27" s="45" t="inlineStr"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>Chung</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>Chọn cách xác thực</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>SSH (khuyến nghị, không nhập mật khẩu mỗi lần) HOẶC HTTPS + Personal Access Token. Làm 1 trong 2 khối dưới.</t>
+        </is>
+      </c>
+      <c r="E28" s="45" t="inlineStr"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>SSH</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>Tạo SSH key</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>ssh-keygen -t ed25519 -C "email-GitHub"  → Enter hết (để mặc định ~/.ssh/id_ed25519)</t>
+        </is>
+      </c>
+      <c r="E29" s="47" t="inlineStr"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>SSH</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Copy public key</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>macOS: pbcopy &lt; ~/.ssh/id_ed25519.pub  •  hoặc mở file .pub và copy toàn bộ</t>
+        </is>
+      </c>
+      <c r="E30" s="47" t="inlineStr"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>SSH</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>Thêm key vào GitHub</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>GitHub → Settings → SSH and GPG keys → New SSH key → dán → Add</t>
+        </is>
+      </c>
+      <c r="E31" s="47" t="inlineStr"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>SSH</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Kiểm tra kết nối</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>ssh -T git@github.com  → hiện "Hi &lt;username&gt;! ... successfully authenticated"</t>
+        </is>
+      </c>
+      <c r="E32" s="47" t="inlineStr"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="B33" s="50" t="inlineStr">
+        <is>
+          <t>PAT</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>Tạo Personal Access Token</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>(thay cho SSH) GitHub → Settings → Developer settings → Personal access tokens → Fine-grained/Tokens (classic) → Generate → scope: repo</t>
+        </is>
+      </c>
+      <c r="E33" s="49" t="inlineStr"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="B34" s="50" t="inlineStr">
+        <is>
+          <t>PAT</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>Dùng token</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>Khi git push qua HTTPS, nhập USERNAME + dán TOKEN vào ô password (không phải mật khẩu tài khoản). Copy token ngay — chỉ hiện 1 lần.</t>
+        </is>
+      </c>
+      <c r="E34" s="49" t="inlineStr"/>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="51" t="n">
+        <v>11</v>
+      </c>
+      <c r="B35" s="52" t="inlineStr">
+        <is>
+          <t>gh CLI</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>(Tùy chọn) Cài GitHub CLI</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>brew install gh  &amp;&amp;  gh auth login  → chọn GitHub.com → xác thực trình duyệt. Cho phép tạo PR bằng lệnh.</t>
+        </is>
+      </c>
+      <c r="E35" s="51" t="inlineStr"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="53" t="n">
+        <v>12</v>
+      </c>
+      <c r="B36" s="54" t="inlineStr">
+        <is>
+          <t>PR flow</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Clone repo</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>SSH: git clone git@github.com:&lt;org&gt;/&lt;repo&gt;.git  •  HTTPS: git clone https://github.com/&lt;org&gt;/&lt;repo&gt;.git  → cd &lt;repo&gt;</t>
+        </is>
+      </c>
+      <c r="E36" s="53" t="inlineStr"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="53" t="n">
+        <v>13</v>
+      </c>
+      <c r="B37" s="54" t="inlineStr">
+        <is>
+          <t>PR flow</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>Tạo nhánh</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>git switch -c feat/my-task   (feat/ | fix/ | chore/ — xem docs/git_workflow.md)</t>
+        </is>
+      </c>
+      <c r="E37" s="53" t="inlineStr"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="53" t="n">
+        <v>14</v>
+      </c>
+      <c r="B38" s="54" t="inlineStr">
+        <is>
+          <t>PR flow</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>Commit thay đổi</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>git add &lt;file&gt;  &amp;&amp;  git commit -m "feat: mô tả ngắn"  (Conventional Commits)</t>
+        </is>
+      </c>
+      <c r="E38" s="53" t="inlineStr"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="53" t="n">
+        <v>15</v>
+      </c>
+      <c r="B39" s="54" t="inlineStr">
+        <is>
+          <t>PR flow</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>Đẩy nhánh lên GitHub</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>git push -u origin feat/my-task</t>
+        </is>
+      </c>
+      <c r="E39" s="53" t="inlineStr"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="53" t="n">
+        <v>16</v>
+      </c>
+      <c r="B40" s="54" t="inlineStr">
+        <is>
+          <t>PR flow</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>Mở Pull Request</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>Web: mở repo trên github.com → banner "Compare &amp; pull request" → base = main, compare = nhánh của bạn. HOẶC lệnh: gh pr create</t>
+        </is>
+      </c>
+      <c r="E40" s="53" t="inlineStr"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="53" t="n">
+        <v>17</v>
+      </c>
+      <c r="B41" s="54" t="inlineStr">
+        <is>
+          <t>PR flow</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>Điền nội dung PR</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>Title theo Conventional Commits; mô tả thay đổi + lý do; link story (VD E.5). KHÔNG dán API key.</t>
+        </is>
+      </c>
+      <c r="E41" s="53" t="inlineStr"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="53" t="n">
+        <v>18</v>
+      </c>
+      <c r="B42" s="54" t="inlineStr">
+        <is>
+          <t>PR flow</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>Chờ CI + review</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>Tab "Actions" phải xanh (chạy pytest + ruff). Chờ reviewer duyệt.</t>
+        </is>
+      </c>
+      <c r="E42" s="53" t="inlineStr"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="53" t="n">
+        <v>19</v>
+      </c>
+      <c r="B43" s="54" t="inlineStr">
+        <is>
+          <t>PR flow</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>Sửa theo góp ý</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>Commit thêm trên cùng nhánh → git push → PR tự cập nhật, không mở PR mới.</t>
+        </is>
+      </c>
+      <c r="E43" s="53" t="inlineStr"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="53" t="n">
+        <v>20</v>
+      </c>
+      <c r="B44" s="54" t="inlineStr">
+        <is>
+          <t>PR flow</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>Merge PR</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>Sau khi approve + CI xanh: nút "Squash and merge" → Confirm → "Delete branch".</t>
+        </is>
+      </c>
+      <c r="E44" s="53" t="inlineStr"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="53" t="n">
+        <v>21</v>
+      </c>
+      <c r="B45" s="54" t="inlineStr">
+        <is>
+          <t>PR flow</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>Đồng bộ local sau merge</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>git switch main  &amp;&amp;  git pull  &amp;&amp;  git branch -d feat/my-task</t>
+        </is>
+      </c>
+      <c r="E45" s="53" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>